--- a/documents/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents/WeValue_현장ACD_메신저템플릿.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lds85\Desktop\임덕수\git\2026-QI\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\임덕수\2026-QI\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29337C38-58DB-4093-8A1A-12F8EAB439BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF1FF0F-99C7-40BA-B367-66EA3AD5365C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="소통메신저 양식 자동완성" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
   <si>
     <t>A(보고)</t>
   </si>
@@ -44,12 +44,6 @@
     <t>현재(상태)</t>
   </si>
   <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
     <t>긴급도</t>
   </si>
   <si>
@@ -59,9 +53,6 @@
     <t>주의</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
     <t>수술중</t>
   </si>
   <si>
@@ -120,23 +111,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>김철수</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>KJS</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
     <t>월일(MMDD)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0227</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>0030</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -201,7 +180,11 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>WeValue_현장ACD_메신저템플릿</t>
+    <t>가나다</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeValue 현장ACD 메신저 템플릿</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -209,6 +192,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="176" formatCode="mmdd\ hh:mm:ss"/>
+    <numFmt numFmtId="177" formatCode="hhmm"/>
+    <numFmt numFmtId="178" formatCode="yyyy\-mm\ hh:mm:ss"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -260,7 +248,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -297,12 +285,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -371,7 +353,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -398,46 +380,132 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="9">
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF00B050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF9900"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF6600"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="0"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FFFF0000"/>
+      </font>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="FFFF9900"/>
+      <color rgb="FFFF6600"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -735,85 +803,93 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K10"/>
-  <sheetFormatPr defaultRowHeight="32.25" customHeight="1" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J10"/>
+  <sheetFormatPr defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" style="4" customWidth="1"/>
-    <col min="2" max="2" width="26" style="4" customWidth="1"/>
-    <col min="3" max="9" width="12.875" style="4" customWidth="1"/>
-    <col min="10" max="10" width="106.125" style="4" customWidth="1"/>
-    <col min="11" max="11" width="100.25" style="12" customWidth="1"/>
+    <col min="1" max="1" width="11.875" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="9.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.25" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.5" style="4" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="22.125" style="4" customWidth="1"/>
+    <col min="10" max="10" width="96.125" style="4" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="100.25" style="4" customWidth="1"/>
     <col min="12" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="B1" s="13"/>
-      <c r="C1" s="13"/>
-      <c r="D1" s="13"/>
-      <c r="E1" s="13"/>
-      <c r="F1" s="13"/>
-      <c r="G1" s="13"/>
-      <c r="H1" s="13"/>
-      <c r="I1" s="13"/>
-      <c r="J1" s="13"/>
-    </row>
-    <row r="2" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+    </row>
+    <row r="2" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="14"/>
       <c r="B2" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="H2" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="I2" s="15"/>
+      <c r="J2" s="15"/>
+    </row>
+    <row r="3" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="15"/>
+      <c r="B3" s="10">
+        <v>1311</v>
+      </c>
+      <c r="C3" s="10">
+        <v>12345678</v>
+      </c>
+      <c r="D3" s="10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E3" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="H2" s="14" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-    </row>
-    <row r="3" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="14"/>
-      <c r="B3" s="15">
-        <v>1311</v>
-      </c>
-      <c r="C3" s="15">
-        <v>12345678</v>
-      </c>
-      <c r="D3" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>32</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>35</v>
-      </c>
-      <c r="H3" s="17" t="str">
-        <f>"["&amp;B3&amp;"]-["&amp;C3&amp;"]-["&amp;D3&amp;"]-["&amp;E3&amp;"]-["&amp;TEXT(F3,"0000")&amp;"]-["&amp;TEXT(G3,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[김철수]-[KJS]-[0227]-[0030]</v>
-      </c>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-    </row>
-    <row r="4" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="F3" s="13" t="str">
+        <f ca="1">TEXT(NOW(), "mmdd")</f>
+        <v>0307</v>
+      </c>
+      <c r="G3" s="12" t="str">
+        <f ca="1">TEXT(NOW(), "hhmm")</f>
+        <v>0023</v>
+      </c>
+      <c r="H3" s="16" t="str">
+        <f ca="1">"["&amp;B3&amp;"]-["&amp;C3&amp;"]-["&amp;D3&amp;"]-["&amp;E3&amp;"]-["&amp;TEXT(F3,"0000")&amp;"]-["&amp;TEXT(G3,"0000")&amp;"]"</f>
+        <v>[1311]-[12345678]-[가나다]-[KJS]-[0307]-[0023]</v>
+      </c>
+      <c r="I3" s="16"/>
+      <c r="J3" s="16"/>
+    </row>
+    <row r="4" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
@@ -821,35 +897,35 @@
         <v>4</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>5</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>6</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="6"/>
+      <c r="B5" s="24"/>
       <c r="C5" s="6"/>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
@@ -858,16 +934,16 @@
       <c r="H5" s="7"/>
       <c r="I5" s="7"/>
       <c r="J5" s="5" t="str">
-        <f>IF($H$3="","", "[A]"&amp;$H$3&amp;" / 지금:"&amp;C5&amp;" / 근거:"&amp;D5&amp;" / 요청:"&amp;E5&amp;" / "&amp;B5)</f>
-        <v xml:space="preserve">[A][1311]-[12345678]-[김철수]-[KJS]-[0227]-[0030] / 지금: / 근거: / 요청: / </v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+        <f ca="1">IF($H$3="","", "[A]"&amp;$H$3&amp;" / 지금:"&amp;C5&amp;" / 근거:"&amp;D5&amp;" / 요청:"&amp;E5&amp;" / "&amp;B5)</f>
+        <v xml:space="preserve">[A][1311]-[12345678]-[가나다]-[KJS]-[0307]-[0023] / 지금: / 근거: / 요청: / </v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
+      <c r="C6" s="11"/>
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="6"/>
@@ -875,11 +951,11 @@
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="5" t="str">
-        <f>IF($H$3="","", "[C]"&amp;$H$3&amp;" / "&amp;IF(F6="","{사유코드}",F6)&amp;" / 다음확인 "&amp;G6&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[김철수]-[KJS]-[0227]-[0030] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+        <f ca="1">IF($H$3="","", "[C]"&amp;$H$3&amp;" / "&amp;IF(F6="","{사유코드}",F6)&amp;" / 다음확인 "&amp;G6&amp;" (전화 1회 후)")</f>
+        <v>[C][1311]-[12345678]-[가나다]-[KJS]-[0307]-[0023] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>2</v>
       </c>
@@ -892,13 +968,13 @@
       <c r="H7" s="6"/>
       <c r="I7" s="6"/>
       <c r="J7" s="5" t="str">
-        <f>IF($H$3="","", "[D]"&amp;$H$3&amp;" / 결과:"&amp;C7&amp;" / 현재:"&amp;H7&amp;" / F/U:"&amp;I7)</f>
-        <v>[D][1311]-[12345678]-[김철수]-[KJS]-[0227]-[0030] / 결과: / 현재: / F/U:</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+        <f ca="1">IF($H$3="","", "[D]"&amp;$H$3&amp;" / 결과:"&amp;C7&amp;" / 현재:"&amp;H7&amp;" / F/U:"&amp;I7)</f>
+        <v>[D][1311]-[12345678]-[가나다]-[KJS]-[0307]-[0023] / 결과: / 현재: / F/U:</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="B8" s="7"/>
       <c r="C8" s="8"/>
@@ -909,11 +985,11 @@
       <c r="H8" s="7"/>
       <c r="I8" s="7"/>
       <c r="J8" s="5" t="str">
-        <f>IF($H$3="","", "(보고)"&amp;$H$3&amp;"/"&amp;C8&amp;IF(C8="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[김철수]-[KJS]-[0227]-[0030]/12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
+        <f ca="1">IF($H$3="","", "(보고)"&amp;$H$3&amp;"/"&amp;C8&amp;IF(C8="","","/")&amp;"12")</f>
+        <v>(보고)[1311]-[12345678]-[가나다]-[KJS]-[0307]-[0023]/12</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="9"/>
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
@@ -925,19 +1001,19 @@
       <c r="I9" s="9"/>
       <c r="J9" s="9"/>
     </row>
-    <row r="10" spans="1:10" ht="32.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="19"/>
-      <c r="J10" s="20"/>
+    <row r="10" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="B10" s="20"/>
+      <c r="C10" s="20"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="20"/>
+      <c r="F10" s="20"/>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="20"/>
+      <c r="J10" s="21"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -948,7 +1024,19 @@
     <mergeCell ref="A10:J10"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
+  <conditionalFormatting sqref="B5">
+    <cfRule type="expression" dxfId="1" priority="3">
+      <formula>B5=10</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="2" priority="2">
+      <formula>B5=4</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>B5=12</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
@@ -990,110 +1078,110 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="G1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2">
         <v>10</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="B2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="G1" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="4" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3">
+        <v>4</v>
+      </c>
+      <c r="B3" t="s">
         <v>12</v>
       </c>
-      <c r="B2" t="s">
+      <c r="D3" s="23"/>
+      <c r="E3" s="23"/>
+      <c r="F3" s="23"/>
+      <c r="G3" s="4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>12</v>
+      </c>
+      <c r="B4" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="11"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D3" s="11"/>
-      <c r="E3" s="11"/>
-      <c r="F3" s="11"/>
-      <c r="G3" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="11"/>
-      <c r="E4" s="11"/>
-      <c r="F4" s="11"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="23"/>
+      <c r="F4" s="23"/>
       <c r="G4" s="4" t="s">
-        <v>47</v>
+        <v>41</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B7" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B8" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B9" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B10" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B11" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B12" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B13" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B14" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/documents/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents/WeValue_현장ACD_메신저템플릿.xlsx
@@ -8,27 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\임덕수\2026-QI\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF1FF0F-99C7-40BA-B367-66EA3AD5365C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB500A6-9A47-43EF-BA37-4294D3F82BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="소통메신저 양식 자동완성" sheetId="2" r:id="rId1"/>
-    <sheet name="02_코드목록" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="02_코드목록" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
   <si>
     <t>A(보고)</t>
   </si>
   <si>
-    <t>C(보호기록)</t>
-  </si>
-  <si>
     <t>D(완료)</t>
   </si>
   <si>
@@ -47,18 +44,12 @@
     <t>긴급도</t>
   </si>
   <si>
-    <t>사유코드(권장)</t>
-  </si>
-  <si>
     <t>주의</t>
   </si>
   <si>
     <t>수술중</t>
   </si>
   <si>
-    <t>엑셀/웹 문서에는 실제 환자정보 입력 금지. (예시/자리표시자만)</t>
-  </si>
-  <si>
     <t>시술중</t>
   </si>
   <si>
@@ -108,10 +99,6 @@
   </si>
   <si>
     <t>교수이름</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>KJS</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -185,6 +172,119 @@
   </si>
   <si>
     <t>WeValue 현장ACD 메신저 템플릿</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>14층 코드</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[CHEMO]</t>
+  </si>
+  <si>
+    <t>항암 특화</t>
+  </si>
+  <si>
+    <t>[BLOOD]</t>
+  </si>
+  <si>
+    <t>수혈 및 혈액</t>
+  </si>
+  <si>
+    <t>[CVR]</t>
+  </si>
+  <si>
+    <t>[LIFE]</t>
+  </si>
+  <si>
+    <t>존엄 및 임종 (LST/DNR)</t>
+  </si>
+  <si>
+    <t>[MEET]</t>
+  </si>
+  <si>
+    <t>보호자 면담</t>
+  </si>
+  <si>
+    <t>[MARROW]</t>
+  </si>
+  <si>
+    <t>골수 검사</t>
+  </si>
+  <si>
+    <t>[ISO]</t>
+  </si>
+  <si>
+    <t>격리 및 역격리</t>
+  </si>
+  <si>
+    <t>엑셀/웹 문서에는 실제 환자정보 입력 금지. (예시/자리표시자만)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>위험 수치 및 Lab (Critical Value Report)</t>
+  </si>
+  <si>
+    <t>[C-Status]</t>
+  </si>
+  <si>
+    <t>상태 변화 (Condition Status)</t>
+  </si>
+  <si>
+    <t>[PAIN]</t>
+  </si>
+  <si>
+    <t>통증 조절 (Pain Management)</t>
+  </si>
+  <si>
+    <t>[OUT]</t>
+  </si>
+  <si>
+    <t>퇴원·전과·사망 관리 (Discharge/Death)</t>
+  </si>
+  <si>
+    <t>141W,142W 전용
+"하이패스" 태그</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>IN-OUT(인계)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(보호기록)-PA</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>C(보호기록)-병동</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>사유코드(권장)-PA</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>사유코드(권장)-병동</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>박재홍</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>확인</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>처방확인</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>자가약소지</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>사진첨부</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -197,7 +297,7 @@
     <numFmt numFmtId="177" formatCode="hhmm"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +347,14 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFF00"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -289,7 +397,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -349,11 +457,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -361,7 +484,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -392,6 +514,24 @@
     <xf numFmtId="178" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -416,28 +556,17 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <font>
         <color theme="0"/>
@@ -464,39 +593,9 @@
       </font>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFF6600"/>
+          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color theme="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FFFF0000"/>
-      </font>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -803,260 +902,320 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:K11"/>
   <sheetFormatPr defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="16.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="13.25" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.5" style="4" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="22.125" style="4" customWidth="1"/>
-    <col min="10" max="10" width="96.125" style="4" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="100.25" style="4" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="4"/>
+    <col min="1" max="1" width="19.375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="21.875" style="3" customWidth="1"/>
+    <col min="3" max="3" width="16.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.625" style="3" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5" style="3" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.125" style="3" customWidth="1"/>
+    <col min="11" max="11" width="96.125" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="100.25" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
-        <v>45</v>
-      </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
-      <c r="I1" s="18"/>
-      <c r="J1" s="18"/>
-    </row>
-    <row r="2" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="14"/>
-      <c r="B2" s="2" t="s">
+    <row r="1" spans="1:11" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="22" t="s">
+        <v>41</v>
+      </c>
+      <c r="B1" s="22"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+    </row>
+    <row r="2" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="19"/>
+      <c r="B2" s="19"/>
+      <c r="C2" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="H2" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="I2" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+    </row>
+    <row r="3" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="9">
+        <v>1311</v>
+      </c>
+      <c r="D3" s="9">
+        <v>12345678</v>
+      </c>
+      <c r="E3" s="9" t="s">
+        <v>40</v>
+      </c>
+      <c r="F3" s="9" t="s">
+        <v>70</v>
+      </c>
+      <c r="G3" s="12" t="str">
+        <f ca="1">TEXT(NOW(), "mmdd")</f>
+        <v>0308</v>
+      </c>
+      <c r="H3" s="11" t="str">
+        <f ca="1">TEXT(NOW(), "hhmm")</f>
+        <v>1922</v>
+      </c>
+      <c r="I3" s="21" t="str">
+        <f ca="1">"["&amp;C3&amp;"]-["&amp;D3&amp;"]-["&amp;E3&amp;"]-["&amp;F3&amp;"]-["&amp;TEXT(G3,"0000")&amp;"]-["&amp;TEXT(H3,"0000")&amp;"]"</f>
+        <v>[1311]-[12345678]-[가나다]-[박재홍]-[0308]-[1922]</v>
+      </c>
+      <c r="J3" s="21"/>
+      <c r="K3" s="21"/>
+    </row>
+    <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>64</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="H2" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="I2" s="15"/>
-      <c r="J2" s="15"/>
-    </row>
-    <row r="3" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="10">
-        <v>1311</v>
-      </c>
-      <c r="C3" s="10">
-        <v>12345678</v>
-      </c>
-      <c r="D3" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E3" s="10" t="s">
-        <v>28</v>
-      </c>
-      <c r="F3" s="13" t="str">
-        <f ca="1">TEXT(NOW(), "mmdd")</f>
-        <v>0307</v>
-      </c>
-      <c r="G3" s="12" t="str">
-        <f ca="1">TEXT(NOW(), "hhmm")</f>
-        <v>0023</v>
-      </c>
-      <c r="H3" s="16" t="str">
-        <f ca="1">"["&amp;B3&amp;"]-["&amp;C3&amp;"]-["&amp;D3&amp;"]-["&amp;E3&amp;"]-["&amp;TEXT(F3,"0000")&amp;"]-["&amp;TEXT(G3,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[가나다]-[KJS]-[0307]-[0023]</v>
-      </c>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-    </row>
-    <row r="4" spans="1:10" ht="49.5" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="24"/>
-      <c r="C5" s="6"/>
-      <c r="D5" s="6"/>
-      <c r="E5" s="6"/>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
-      <c r="H5" s="7"/>
-      <c r="I5" s="7"/>
-      <c r="J5" s="5" t="str">
-        <f ca="1">IF($H$3="","", "[A]"&amp;$H$3&amp;" / 지금:"&amp;C5&amp;" / 근거:"&amp;D5&amp;" / 요청:"&amp;E5&amp;" / "&amp;B5)</f>
-        <v xml:space="preserve">[A][1311]-[12345678]-[가나다]-[KJS]-[0307]-[0023] / 지금: / 근거: / 요청: / </v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="5"/>
+      <c r="C5" s="5">
+        <v>12</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="G5" s="6"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="6"/>
+      <c r="J5" s="6"/>
+      <c r="K5" s="4" t="str">
+        <f ca="1">B5&amp;IF($I$3="","", "[A]"&amp;$I$3&amp;" / 지금:"&amp;D5&amp;" / 근거:"&amp;E5&amp;" / 요청:"&amp;F5&amp;" / "&amp;C5)</f>
+        <v>[A][1311]-[12345678]-[가나다]-[박재홍]-[0308]-[1922] / 지금:자가약소지 / 근거: / 요청:사진첨부 / 12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" s="6"/>
+      <c r="C6" s="6"/>
+      <c r="D6" s="10"/>
+      <c r="E6" s="6"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="6"/>
+      <c r="J6" s="6"/>
+      <c r="K6" s="4" t="str">
+        <f ca="1">IF($I$3="","", "[C]"&amp;$I$3&amp;" / "&amp;IF(G6="","{사유코드}",G6)&amp;" / 다음확인 "&amp;H6&amp;" (전화 1회 후)")</f>
+        <v>[C][1311]-[12345678]-[가나다]-[박재홍]-[0308]-[1922] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" s="6"/>
+      <c r="C7" s="6"/>
+      <c r="D7" s="10"/>
+      <c r="E7" s="6"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="6"/>
+      <c r="J7" s="6"/>
+      <c r="K7" s="4" t="str">
+        <f ca="1">IF($I$3="","", "[C]"&amp;$I$3&amp;" / "&amp;IF(G7="","{사유코드}",G7)&amp;" / 다음확인 "&amp;H7&amp;" (전화 1회 후)")</f>
+        <v>[C][1311]-[12345678]-[가나다]-[박재홍]-[0308]-[1922] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="6"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="5" t="str">
-        <f ca="1">IF($H$3="","", "[C]"&amp;$H$3&amp;" / "&amp;IF(F6="","{사유코드}",F6)&amp;" / 다음확인 "&amp;G6&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[KJS]-[0307]-[0023] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B7" s="7"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="6"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="5" t="str">
-        <f ca="1">IF($H$3="","", "[D]"&amp;$H$3&amp;" / 결과:"&amp;C7&amp;" / 현재:"&amp;H7&amp;" / F/U:"&amp;I7)</f>
-        <v>[D][1311]-[12345678]-[가나다]-[KJS]-[0307]-[0023] / 결과: / 현재: / F/U:</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B8" s="7"/>
-      <c r="C8" s="8"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
-      <c r="J8" s="5" t="str">
-        <f ca="1">IF($H$3="","", "(보고)"&amp;$H$3&amp;"/"&amp;C8&amp;IF(C8="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[가나다]-[KJS]-[0307]-[0023]/12</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="9"/>
-      <c r="B9" s="9"/>
-      <c r="C9" s="9"/>
-      <c r="D9" s="9"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9"/>
-      <c r="H9" s="9"/>
-      <c r="I9" s="9"/>
-      <c r="J9" s="9"/>
-    </row>
-    <row r="10" spans="1:10" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="19" t="s">
-        <v>43</v>
-      </c>
-      <c r="B10" s="20"/>
-      <c r="C10" s="20"/>
-      <c r="D10" s="20"/>
-      <c r="E10" s="20"/>
-      <c r="F10" s="20"/>
-      <c r="G10" s="20"/>
-      <c r="H10" s="20"/>
-      <c r="I10" s="20"/>
-      <c r="J10" s="21"/>
+      <c r="B8" s="6"/>
+      <c r="C8" s="6"/>
+      <c r="D8" s="5" t="s">
+        <v>71</v>
+      </c>
+      <c r="E8" s="6"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="6"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="J8" s="5"/>
+      <c r="K8" s="4" t="str">
+        <f ca="1">IF($I$3="","", "[D]"&amp;$I$3&amp;" / 결과:"&amp;D8&amp;" / 현재:"&amp;I8&amp;" / F/U:"&amp;J8)</f>
+        <v>[D][1311]-[12345678]-[가나다]-[박재홍]-[0308]-[1922] / 결과:확인 / 현재:처방확인 / F/U:</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B9" s="6"/>
+      <c r="C9" s="6"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="6"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="6"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="6"/>
+      <c r="J9" s="6"/>
+      <c r="K9" s="4" t="str">
+        <f ca="1">IF($I$3="","", "(보고)"&amp;$I$3&amp;"/"&amp;D9&amp;IF(D9="","","/")&amp;"12")</f>
+        <v>(보고)[1311]-[12345678]-[가나다]-[박재홍]-[0308]-[1922]/12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="8"/>
+      <c r="B10" s="8"/>
+      <c r="C10" s="8"/>
+      <c r="D10" s="8"/>
+      <c r="E10" s="8"/>
+      <c r="F10" s="8"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="8"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="8"/>
+      <c r="K10" s="8"/>
+    </row>
+    <row r="11" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B11" s="25"/>
+      <c r="C11" s="25"/>
+      <c r="D11" s="25"/>
+      <c r="E11" s="25"/>
+      <c r="F11" s="25"/>
+      <c r="G11" s="25"/>
+      <c r="H11" s="25"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="25"/>
+      <c r="K11" s="26"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
     <mergeCell ref="A2:A3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="A10:J10"/>
+    <mergeCell ref="I3:K3"/>
+    <mergeCell ref="I2:K2"/>
+    <mergeCell ref="A1:K1"/>
+    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="B2:B3"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="B5">
-    <cfRule type="expression" dxfId="1" priority="3">
-      <formula>B5=10</formula>
+  <conditionalFormatting sqref="B5:C5">
+    <cfRule type="expression" dxfId="2" priority="1">
+      <formula>B5=12</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="2" priority="2">
+    <cfRule type="expression" dxfId="1" priority="2">
       <formula>B5=4</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="0" priority="1">
-      <formula>B5=12</formula>
+    <cfRule type="expression" dxfId="0" priority="3">
+      <formula>B5=10</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>B5 B8</xm:sqref>
+          <xm:sqref>C5 C9</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$2:$B$14</xm:f>
           </x14:formula1>
-          <xm:sqref>F5:F7</xm:sqref>
+          <xm:sqref>G5 G8</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{72FFAC11-A338-427E-AF73-F7D83A85893C}">
           <x14:formula1>
-            <xm:f>'02_코드목록'!$G$2:$G$4</xm:f>
+            <xm:f>'02_코드목록'!$J$2:$J$4</xm:f>
           </x14:formula1>
-          <xm:sqref>C8</xm:sqref>
+          <xm:sqref>D9</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{54F24218-F1A5-4C39-A88F-EBBD79DE5CE8}">
+          <x14:formula1>
+            <xm:f>'02_코드목록'!$L$2:$L$11</xm:f>
+          </x14:formula1>
+          <xm:sqref>B5</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{0D061B27-2ED0-4A89-8EF3-BCF08CD5E27F}">
+          <x14:formula1>
+            <xm:f>'02_코드목록'!$B$2:$B$15</xm:f>
+          </x14:formula1>
+          <xm:sqref>G6</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" xr:uid="{06472377-7060-4FB5-A3C2-0B85F9411171}">
+          <x14:formula1>
+            <xm:f>'02_코드목록'!$D$2</xm:f>
+          </x14:formula1>
+          <xm:sqref>G7</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1067,126 +1226,213 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="18" customWidth="1"/>
-    <col min="3" max="3" width="2" customWidth="1"/>
-    <col min="7" max="7" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12" style="14" customWidth="1"/>
+    <col min="2" max="2" width="18" style="14" customWidth="1"/>
+    <col min="3" max="3" width="2" style="14" customWidth="1"/>
+    <col min="4" max="4" width="19" style="14" customWidth="1"/>
+    <col min="5" max="5" width="2" style="14" customWidth="1"/>
+    <col min="6" max="9" width="9" style="14"/>
+    <col min="10" max="10" width="17.25" style="14" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.25" style="14" customWidth="1"/>
+    <col min="12" max="12" width="11.375" style="14" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="38" style="14" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="14"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A1" s="13" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="D1" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="F1" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="G1" s="15"/>
+      <c r="H1" s="15"/>
+      <c r="J1" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="15"/>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A2" s="15">
+        <v>10</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D2" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="F2" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="J2" s="16" t="s">
+        <v>35</v>
+      </c>
+      <c r="K2" s="17"/>
+      <c r="L2" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="M2" s="15" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A3" s="15">
+        <v>4</v>
+      </c>
+      <c r="B3" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="G1" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2">
+      <c r="F3" s="28"/>
+      <c r="G3" s="28"/>
+      <c r="H3" s="28"/>
+      <c r="J3" s="16" t="s">
+        <v>36</v>
+      </c>
+      <c r="K3" s="17"/>
+      <c r="L3" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="M3" s="15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A4" s="15">
+        <v>12</v>
+      </c>
+      <c r="B4" s="15" t="s">
         <v>10</v>
       </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="D2" s="22" t="s">
+      <c r="F4" s="28"/>
+      <c r="G4" s="28"/>
+      <c r="H4" s="28"/>
+      <c r="J4" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="K4" s="17"/>
+      <c r="L4" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="15" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B5" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="4" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="L5" s="15" t="s">
+        <v>48</v>
+      </c>
+      <c r="M5" s="15" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B6" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="23"/>
-      <c r="E3" s="23"/>
-      <c r="F3" s="23"/>
-      <c r="G3" s="4" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4">
-        <v>12</v>
-      </c>
-      <c r="B4" t="s">
+      <c r="L6" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="M6" s="15" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B7" s="15" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="23"/>
-      <c r="E4" s="23"/>
-      <c r="F4" s="23"/>
-      <c r="G4" s="4" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B5" t="s">
+      <c r="L7" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="M7" s="15" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B8" s="15" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B6" t="s">
+      <c r="L8" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B9" s="15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B7" t="s">
+      <c r="L9" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="M9" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B10" s="15" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B8" t="s">
+      <c r="L10" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B11" s="15" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B9" t="s">
+      <c r="L11" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="M11" s="15" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B12" s="15" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B10" t="s">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B13" s="15" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B11" t="s">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B14" s="15" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B13" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="B14" t="s">
-        <v>23</v>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="B15" s="15" t="s">
+        <v>65</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="D2:F4"/>
+    <mergeCell ref="F2:H4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/documents/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents/WeValue_현장ACD_메신저템플릿.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\임덕수\2026-QI\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lds85\Desktop\임덕수\git\2026-QI\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB500A6-9A47-43EF-BA37-4294D3F82BD4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC2D880-DF5A-492D-98B1-188B5289CF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="소통메신저 양식 자동완성" sheetId="2" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
   <si>
     <t>A(보고)</t>
   </si>
@@ -268,10 +268,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>박재홍</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>확인</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -280,11 +276,7 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>자가약소지</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>사진첨부</t>
+    <t>박OO</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -975,7 +967,7 @@
         <v>40</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G3" s="12" t="str">
         <f ca="1">TEXT(NOW(), "mmdd")</f>
@@ -983,11 +975,11 @@
       </c>
       <c r="H3" s="11" t="str">
         <f ca="1">TEXT(NOW(), "hhmm")</f>
-        <v>1922</v>
+        <v>2137</v>
       </c>
       <c r="I3" s="21" t="str">
         <f ca="1">"["&amp;C3&amp;"]-["&amp;D3&amp;"]-["&amp;E3&amp;"]-["&amp;F3&amp;"]-["&amp;TEXT(G3,"0000")&amp;"]-["&amp;TEXT(H3,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[가나다]-[박재홍]-[0308]-[1922]</v>
+        <v>[1311]-[12345678]-[가나다]-[박OO]-[0308]-[2137]</v>
       </c>
       <c r="J3" s="21"/>
       <c r="K3" s="21"/>
@@ -1035,20 +1027,16 @@
       <c r="C5" s="5">
         <v>12</v>
       </c>
-      <c r="D5" s="5" t="s">
-        <v>73</v>
-      </c>
+      <c r="D5" s="5"/>
       <c r="E5" s="5"/>
-      <c r="F5" s="5" t="s">
-        <v>74</v>
-      </c>
+      <c r="F5" s="5"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
       <c r="I5" s="6"/>
       <c r="J5" s="6"/>
       <c r="K5" s="4" t="str">
         <f ca="1">B5&amp;IF($I$3="","", "[A]"&amp;$I$3&amp;" / 지금:"&amp;D5&amp;" / 근거:"&amp;E5&amp;" / 요청:"&amp;F5&amp;" / "&amp;C5)</f>
-        <v>[A][1311]-[12345678]-[가나다]-[박재홍]-[0308]-[1922] / 지금:자가약소지 / 근거: / 요청:사진첨부 / 12</v>
+        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2137] / 지금: / 근거: / 요청: / 12</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1066,7 +1054,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="4" t="str">
         <f ca="1">IF($I$3="","", "[C]"&amp;$I$3&amp;" / "&amp;IF(G6="","{사유코드}",G6)&amp;" / 다음확인 "&amp;H6&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박재홍]-[0308]-[1922] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2137] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1084,7 +1072,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="4" t="str">
         <f ca="1">IF($I$3="","", "[C]"&amp;$I$3&amp;" / "&amp;IF(G7="","{사유코드}",G7)&amp;" / 다음확인 "&amp;H7&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박재홍]-[0308]-[1922] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2137] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1094,19 +1082,19 @@
       <c r="B8" s="6"/>
       <c r="C8" s="6"/>
       <c r="D8" s="5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="E8" s="6"/>
       <c r="F8" s="6"/>
       <c r="G8" s="6"/>
       <c r="H8" s="6"/>
       <c r="I8" s="5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="4" t="str">
         <f ca="1">IF($I$3="","", "[D]"&amp;$I$3&amp;" / 결과:"&amp;D8&amp;" / 현재:"&amp;I8&amp;" / F/U:"&amp;J8)</f>
-        <v>[D][1311]-[12345678]-[가나다]-[박재홍]-[0308]-[1922] / 결과:확인 / 현재:처방확인 / F/U:</v>
+        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2137] / 결과:확인 / 현재:처방확인 / F/U:</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1124,7 +1112,7 @@
       <c r="J9" s="6"/>
       <c r="K9" s="4" t="str">
         <f ca="1">IF($I$3="","", "(보고)"&amp;$I$3&amp;"/"&amp;D9&amp;IF(D9="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[가나다]-[박재홍]-[0308]-[1922]/12</v>
+        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0308]-[2137]/12</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">

--- a/documents/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents/WeValue_현장ACD_메신저템플릿.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lds85\Desktop\임덕수\git\2026-QI\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AC2D880-DF5A-492D-98B1-188B5289CF1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4224BF-7893-43DC-BA6B-871EA31E5C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="소통메신저 양식 자동완성" sheetId="2" r:id="rId1"/>
-    <sheet name="02_코드목록" sheetId="3" r:id="rId2"/>
+    <sheet name="02_코드목록" sheetId="3" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -975,11 +975,11 @@
       </c>
       <c r="H3" s="11" t="str">
         <f ca="1">TEXT(NOW(), "hhmm")</f>
-        <v>2137</v>
+        <v>2211</v>
       </c>
       <c r="I3" s="21" t="str">
         <f ca="1">"["&amp;C3&amp;"]-["&amp;D3&amp;"]-["&amp;E3&amp;"]-["&amp;F3&amp;"]-["&amp;TEXT(G3,"0000")&amp;"]-["&amp;TEXT(H3,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[가나다]-[박OO]-[0308]-[2137]</v>
+        <v>[1311]-[12345678]-[가나다]-[박OO]-[0308]-[2211]</v>
       </c>
       <c r="J3" s="21"/>
       <c r="K3" s="21"/>
@@ -1036,7 +1036,7 @@
       <c r="J5" s="6"/>
       <c r="K5" s="4" t="str">
         <f ca="1">B5&amp;IF($I$3="","", "[A]"&amp;$I$3&amp;" / 지금:"&amp;D5&amp;" / 근거:"&amp;E5&amp;" / 요청:"&amp;F5&amp;" / "&amp;C5)</f>
-        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2137] / 지금: / 근거: / 요청: / 12</v>
+        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2211] / 지금: / 근거: / 요청: / 12</v>
       </c>
     </row>
     <row r="6" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1054,7 +1054,7 @@
       <c r="J6" s="6"/>
       <c r="K6" s="4" t="str">
         <f ca="1">IF($I$3="","", "[C]"&amp;$I$3&amp;" / "&amp;IF(G6="","{사유코드}",G6)&amp;" / 다음확인 "&amp;H6&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2137] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2211] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1072,7 +1072,7 @@
       <c r="J7" s="6"/>
       <c r="K7" s="4" t="str">
         <f ca="1">IF($I$3="","", "[C]"&amp;$I$3&amp;" / "&amp;IF(G7="","{사유코드}",G7)&amp;" / 다음확인 "&amp;H7&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2137] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2211] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="8" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1094,7 +1094,7 @@
       <c r="J8" s="5"/>
       <c r="K8" s="4" t="str">
         <f ca="1">IF($I$3="","", "[D]"&amp;$I$3&amp;" / 결과:"&amp;D8&amp;" / 현재:"&amp;I8&amp;" / F/U:"&amp;J8)</f>
-        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2137] / 결과:확인 / 현재:처방확인 / F/U:</v>
+        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2211] / 결과:확인 / 현재:처방확인 / F/U:</v>
       </c>
     </row>
     <row r="9" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -1112,7 +1112,7 @@
       <c r="J9" s="6"/>
       <c r="K9" s="4" t="str">
         <f ca="1">IF($I$3="","", "(보고)"&amp;$I$3&amp;"/"&amp;D9&amp;IF(D9="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0308]-[2137]/12</v>
+        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0308]-[2211]/12</v>
       </c>
     </row>
     <row r="10" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">

--- a/documents/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents/WeValue_현장ACD_메신저템플릿.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lds85\Desktop\임덕수\git\2026-QI\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahee\Desktop\GitHub동기화폴더\2026-QI\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A4224BF-7893-43DC-BA6B-871EA31E5C85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEA8F8F-03A0-499B-B85A-D96A9684CFB6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
   <si>
     <t>A(보고)</t>
   </si>
@@ -277,6 +277,22 @@
   </si>
   <si>
     <t>박OO</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>야간이음기록</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>조치</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[D]현재상태</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -289,7 +305,7 @@
     <numFmt numFmtId="177" formatCode="hhmm"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -347,6 +363,14 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -389,64 +413,12 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="12">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF9E9E9E"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF9E9E9E"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF9E9E9E"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF9E9E9E"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF9E9E9E"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF9E9E9E"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF9E9E9E"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF9E9E9E"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF9E9E9E"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF9E9E9E"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF9E9E9E"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF9E9E9E"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -464,94 +436,234 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF9E9E9E"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF9E9E9E"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9E9E9E"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9E9E9E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9E9E9E"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF9E9E9E"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF9E9E9E"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9E9E9E"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.499984740745262"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="FF9E9E9E"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="22" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
   </cellXfs>
@@ -894,263 +1006,308 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K11"/>
+  <dimension ref="A1:K13"/>
   <sheetFormatPr defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.375" style="3" customWidth="1"/>
-    <col min="2" max="2" width="21.875" style="3" customWidth="1"/>
-    <col min="3" max="3" width="16.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.625" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.125" style="3" customWidth="1"/>
-    <col min="11" max="11" width="96.125" style="3" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="100.25" style="3" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="3"/>
+    <col min="1" max="1" width="19.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="21.875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="16.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="22.125" style="1" customWidth="1"/>
+    <col min="11" max="11" width="96.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="100.25" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="22"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
     </row>
     <row r="2" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="2" t="s">
+      <c r="A2" s="21"/>
+      <c r="B2" s="21"/>
+      <c r="C2" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="7" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="G2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="H2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="20" t="s">
+      <c r="I2" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="20"/>
-      <c r="K2" s="20"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
     </row>
     <row r="3" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="20"/>
-      <c r="B3" s="20"/>
-      <c r="C3" s="9">
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="11">
         <v>1311</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="11">
         <v>12345678</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="E3" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="9" t="s">
+      <c r="F3" s="11" t="s">
         <v>72</v>
       </c>
       <c r="G3" s="12" t="str">
         <f ca="1">TEXT(NOW(), "mmdd")</f>
-        <v>0308</v>
-      </c>
-      <c r="H3" s="11" t="str">
+        <v>0315</v>
+      </c>
+      <c r="H3" s="13" t="str">
         <f ca="1">TEXT(NOW(), "hhmm")</f>
-        <v>2211</v>
-      </c>
-      <c r="I3" s="21" t="str">
+        <v>0003</v>
+      </c>
+      <c r="I3" s="23" t="str">
         <f ca="1">"["&amp;C3&amp;"]-["&amp;D3&amp;"]-["&amp;E3&amp;"]-["&amp;F3&amp;"]-["&amp;TEXT(G3,"0000")&amp;"]-["&amp;TEXT(H3,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[가나다]-[박OO]-[0308]-[2211]</v>
-      </c>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
-    </row>
-    <row r="4" spans="1:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="A4" s="2" t="s">
+        <v>[1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003]</v>
+      </c>
+      <c r="J3" s="23"/>
+      <c r="K3" s="23"/>
+    </row>
+    <row r="4" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="7" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="H4" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="2" t="s">
+      <c r="I4" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="K4" s="7" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="5"/>
-      <c r="C5" s="5">
+      <c r="B5" s="16"/>
+      <c r="C5" s="16">
         <v>12</v>
       </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="5"/>
-      <c r="G5" s="6"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="6"/>
-      <c r="J5" s="6"/>
-      <c r="K5" s="4" t="str">
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="18" t="str">
         <f ca="1">B5&amp;IF($I$3="","", "[A]"&amp;$I$3&amp;" / 지금:"&amp;D5&amp;" / 근거:"&amp;E5&amp;" / 요청:"&amp;F5&amp;" / "&amp;C5)</f>
-        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2211] / 지금: / 근거: / 요청: / 12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
+        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003] / 지금: / 근거: / 요청: / 12</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="15" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="6"/>
-      <c r="C6" s="6"/>
-      <c r="D6" s="10"/>
-      <c r="E6" s="6"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="6"/>
-      <c r="J6" s="6"/>
-      <c r="K6" s="4" t="str">
+      <c r="B6" s="17"/>
+      <c r="C6" s="17"/>
+      <c r="D6" s="19"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="18" t="str">
         <f ca="1">IF($I$3="","", "[C]"&amp;$I$3&amp;" / "&amp;IF(G6="","{사유코드}",G6)&amp;" / 다음확인 "&amp;H6&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2211] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="15" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="6"/>
-      <c r="C7" s="6"/>
-      <c r="D7" s="10"/>
-      <c r="E7" s="6"/>
-      <c r="F7" s="6"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6"/>
-      <c r="J7" s="6"/>
-      <c r="K7" s="4" t="str">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="17"/>
+      <c r="F7" s="17"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17"/>
+      <c r="J7" s="17"/>
+      <c r="K7" s="18" t="str">
         <f ca="1">IF($I$3="","", "[C]"&amp;$I$3&amp;" / "&amp;IF(G7="","{사유코드}",G7)&amp;" / 다음확인 "&amp;H7&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2211] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="6"/>
-      <c r="C8" s="6"/>
-      <c r="D8" s="5" t="s">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="16" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="6"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="6"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="5" t="s">
+      <c r="E8" s="17"/>
+      <c r="F8" s="17"/>
+      <c r="G8" s="17"/>
+      <c r="H8" s="17"/>
+      <c r="I8" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="5"/>
-      <c r="K8" s="4" t="str">
+      <c r="J8" s="16"/>
+      <c r="K8" s="18" t="str">
         <f ca="1">IF($I$3="","", "[D]"&amp;$I$3&amp;" / 결과:"&amp;D8&amp;" / 현재:"&amp;I8&amp;" / F/U:"&amp;J8)</f>
-        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0308]-[2211] / 결과:확인 / 현재:처방확인 / F/U:</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
+        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003] / 결과:확인 / 현재:처방확인 / F/U:</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="6"/>
-      <c r="C9" s="6"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="6"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="6"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="6"/>
-      <c r="J9" s="6"/>
-      <c r="K9" s="4" t="str">
+      <c r="B9" s="17"/>
+      <c r="C9" s="17"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="17"/>
+      <c r="F9" s="17"/>
+      <c r="G9" s="17"/>
+      <c r="H9" s="17"/>
+      <c r="I9" s="17"/>
+      <c r="J9" s="17"/>
+      <c r="K9" s="18" t="str">
         <f ca="1">IF($I$3="","", "(보고)"&amp;$I$3&amp;"/"&amp;D9&amp;IF(D9="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0308]-[2211]/12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="8"/>
-      <c r="B10" s="8"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="8"/>
-      <c r="K10" s="8"/>
-    </row>
-    <row r="11" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="24" t="s">
+        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003]/12</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B10" s="29" t="s">
+        <v>74</v>
+      </c>
+      <c r="C10" s="29"/>
+      <c r="D10" s="22" t="s">
+        <v>75</v>
+      </c>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="7"/>
+    </row>
+    <row r="11" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="15" t="s">
+        <v>73</v>
+      </c>
+      <c r="B11" s="31"/>
+      <c r="C11" s="32"/>
+      <c r="D11" s="30"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="30"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="30"/>
+      <c r="I11" s="30"/>
+      <c r="J11" s="30"/>
+      <c r="K11" s="18" t="str">
+        <f ca="1">IF($I$3="","", "[A][야간이음기록]"&amp;$I$3&amp;"/지금:"&amp;B11&amp;"/조치:"&amp;D11&amp;"/[D]"&amp;D11&amp;H11)</f>
+        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003]/지금:/조치:/[D]</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="8"/>
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="8"/>
+      <c r="I12" s="8"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="26" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="25"/>
-      <c r="C11" s="25"/>
-      <c r="D11" s="25"/>
-      <c r="E11" s="25"/>
-      <c r="F11" s="25"/>
-      <c r="G11" s="25"/>
-      <c r="H11" s="25"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="25"/>
-      <c r="K11" s="26"/>
+      <c r="B13" s="27"/>
+      <c r="C13" s="27"/>
+      <c r="D13" s="27"/>
+      <c r="E13" s="27"/>
+      <c r="F13" s="27"/>
+      <c r="G13" s="27"/>
+      <c r="H13" s="27"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="27"/>
+      <c r="K13" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="12">
     <mergeCell ref="A2:A3"/>
     <mergeCell ref="I3:K3"/>
     <mergeCell ref="I2:K2"/>
     <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A11:K11"/>
+    <mergeCell ref="A13:K13"/>
     <mergeCell ref="B2:B3"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="D10:G10"/>
+    <mergeCell ref="H10:J10"/>
+    <mergeCell ref="D11:G11"/>
+    <mergeCell ref="H11:J11"/>
+    <mergeCell ref="B11:C11"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
   <conditionalFormatting sqref="B5:C5">
@@ -1217,204 +1374,204 @@
   <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="12" style="14" customWidth="1"/>
-    <col min="2" max="2" width="18" style="14" customWidth="1"/>
-    <col min="3" max="3" width="2" style="14" customWidth="1"/>
-    <col min="4" max="4" width="19" style="14" customWidth="1"/>
-    <col min="5" max="5" width="2" style="14" customWidth="1"/>
-    <col min="6" max="9" width="9" style="14"/>
-    <col min="10" max="10" width="17.25" style="14" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="17.25" style="14" customWidth="1"/>
-    <col min="12" max="12" width="11.375" style="14" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="38" style="14" bestFit="1" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="14"/>
+    <col min="1" max="1" width="12" style="3" customWidth="1"/>
+    <col min="2" max="2" width="18" style="3" customWidth="1"/>
+    <col min="3" max="3" width="2" style="3" customWidth="1"/>
+    <col min="4" max="4" width="19" style="3" customWidth="1"/>
+    <col min="5" max="5" width="2" style="3" customWidth="1"/>
+    <col min="6" max="9" width="9" style="3"/>
+    <col min="10" max="10" width="17.25" style="3" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="17.25" style="3" customWidth="1"/>
+    <col min="12" max="12" width="11.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="38" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="13" t="s">
+      <c r="F1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="J1" s="15" t="s">
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="J1" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="15" t="s">
+      <c r="L1" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="M1" s="15"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="15">
+      <c r="A2" s="4">
         <v>10</v>
       </c>
-      <c r="B2" s="15" t="s">
+      <c r="B2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="15" t="s">
+      <c r="D2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="J2" s="16" t="s">
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="J2" s="5" t="s">
         <v>35</v>
       </c>
-      <c r="K2" s="17"/>
-      <c r="L2" s="15" t="s">
+      <c r="K2" s="6"/>
+      <c r="L2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="4" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="15">
+      <c r="A3" s="4">
         <v>4</v>
       </c>
-      <c r="B3" s="15" t="s">
+      <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="28"/>
-      <c r="G3" s="28"/>
-      <c r="H3" s="28"/>
-      <c r="J3" s="16" t="s">
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
+      <c r="H3" s="34"/>
+      <c r="J3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="K3" s="17"/>
-      <c r="L3" s="15" t="s">
+      <c r="K3" s="6"/>
+      <c r="L3" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="4" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A4" s="15">
+      <c r="A4" s="4">
         <v>12</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="28"/>
-      <c r="G4" s="28"/>
-      <c r="H4" s="28"/>
-      <c r="J4" s="16" t="s">
+      <c r="F4" s="34"/>
+      <c r="G4" s="34"/>
+      <c r="H4" s="34"/>
+      <c r="J4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="K4" s="17"/>
-      <c r="L4" s="15" t="s">
+      <c r="K4" s="6"/>
+      <c r="L4" s="4" t="s">
         <v>47</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="4" t="s">
         <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="4" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B6" s="15" t="s">
+      <c r="B6" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="4" t="s">
         <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B7" s="15" t="s">
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="L7" s="15" t="s">
+      <c r="L7" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="M7" s="15" t="s">
+      <c r="M7" s="4" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B8" s="15" t="s">
+      <c r="B8" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="L8" s="15" t="s">
+      <c r="L8" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="M8" s="15" t="s">
+      <c r="M8" s="4" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="L9" s="15" t="s">
+      <c r="L9" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="M9" s="15" t="s">
+      <c r="M9" s="4" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B10" s="15" t="s">
+      <c r="B10" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="15" t="s">
+      <c r="L10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="M10" s="15" t="s">
+      <c r="M10" s="4" t="s">
         <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B11" s="15" t="s">
+      <c r="B11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="L11" s="15" t="s">
+      <c r="L11" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="M11" s="15" t="s">
+      <c r="M11" s="4" t="s">
         <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B12" s="15" t="s">
+      <c r="B12" s="4" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B13" s="15" t="s">
+      <c r="B13" s="4" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="4" t="s">
         <v>20</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="B15" s="15" t="s">
+      <c r="B15" s="4" t="s">
         <v>65</v>
       </c>
     </row>

--- a/documents/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents/WeValue_현장ACD_메신저템플릿.xlsx
@@ -8,20 +8,202 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahee\Desktop\GitHub동기화폴더\2026-QI\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AEA8F8F-03A0-499B-B85A-D96A9684CFB6}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850E0E1A-E545-4AED-96A0-5C438052D32B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="소통메신저 양식 자동완성" sheetId="2" r:id="rId1"/>
-    <sheet name="02_코드목록" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="02_코드목록" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>rahee</author>
+  </authors>
+  <commentList>
+    <comment ref="L3" authorId="0" shapeId="0" xr:uid="{90FACE3A-7ACC-4375-84D2-A8192ABCBC10}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>노란색</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>셀은</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>모두</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>복사하여</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>대화방에</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>붙여넣기에</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>사용하는</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="돋움"/>
+            <family val="3"/>
+            <charset val="129"/>
+          </rPr>
+          <t>용도입니다</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">. </t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="94">
   <si>
     <t>A(보고)</t>
   </si>
@@ -293,6 +475,73 @@
   </si>
   <si>
     <t>[D]현재상태</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>소속병동</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>근무</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>팀</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>병동간호사</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>소속과</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>담당교수님</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>대화방 프로필 설정</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>CaseId</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>데이</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이브닝</t>
+  </si>
+  <si>
+    <t>이브닝</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>나이트</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>KJS</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>ENT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이름</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>이OO</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -305,7 +554,7 @@
     <numFmt numFmtId="177" formatCode="hhmm"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\ hh:mm:ss"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -371,8 +620,53 @@
       <family val="3"/>
       <charset val="129"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color rgb="FFFF0000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -412,8 +706,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="12">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -438,101 +738,29 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FF9E9E9E"/>
+        <color indexed="64"/>
       </left>
       <right style="thin">
-        <color rgb="FF9E9E9E"/>
+        <color indexed="64"/>
       </right>
       <top style="thin">
-        <color rgb="FF9E9E9E"/>
+        <color indexed="64"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="thin">
-        <color rgb="FF9E9E9E"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </right>
       <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF9E9E9E"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF9E9E9E"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF9E9E9E"/>
-      </top>
-      <bottom style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -542,9 +770,7 @@
       </left>
       <right/>
       <top/>
-      <bottom style="thin">
-        <color rgb="FF9E9E9E"/>
-      </bottom>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -553,8 +779,69 @@
         <color theme="0" tint="-0.499984740745262"/>
       </right>
       <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top/>
       <bottom style="thin">
-        <color rgb="FF9E9E9E"/>
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.249977111117893"/>
       </bottom>
       <diagonal/>
     </border>
@@ -562,7 +849,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -582,89 +869,134 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="22" fontId="0" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1004,363 +1336,481 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K13"/>
+  <dimension ref="B1:L18"/>
   <sheetFormatPr defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.375" style="1" customWidth="1"/>
-    <col min="2" max="2" width="21.875" style="1" customWidth="1"/>
-    <col min="3" max="3" width="16.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="13.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.5" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.125" style="1" customWidth="1"/>
-    <col min="11" max="11" width="96.125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="100.25" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="4.75" style="1" customWidth="1"/>
+    <col min="2" max="2" width="19.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="21.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="16.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.25" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="10.5" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22.125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="96.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="100.25" style="1" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="24" t="s">
+    <row r="1" spans="2:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-    </row>
-    <row r="2" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="7" t="s">
+      <c r="C1" s="10"/>
+      <c r="D1" s="11"/>
+      <c r="E1" s="11"/>
+      <c r="F1" s="11"/>
+      <c r="G1" s="11"/>
+      <c r="H1" s="11"/>
+      <c r="I1" s="11"/>
+      <c r="J1" s="11"/>
+      <c r="K1" s="11"/>
+      <c r="L1" s="11"/>
+    </row>
+    <row r="2" spans="2:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C2" s="12"/>
+      <c r="D2" s="12"/>
+      <c r="E2" s="12"/>
+      <c r="F2" s="12"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="12"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="12"/>
+      <c r="K2" s="12"/>
+      <c r="L2" s="12"/>
+    </row>
+    <row r="3" spans="2:12" s="9" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B3" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="D3" s="14">
+        <v>123</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="F3" s="47" t="s">
+        <v>87</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="H3" s="14">
+        <v>12</v>
+      </c>
+      <c r="I3" s="15" t="s">
+        <v>92</v>
+      </c>
+      <c r="J3" s="14" t="s">
+        <v>93</v>
+      </c>
+      <c r="K3" s="15"/>
+      <c r="L3" s="16" t="str">
+        <f>"["&amp;D3&amp;"/"&amp;F3&amp;"/"&amp;H3&amp;"] "&amp;J3</f>
+        <v>[123/이브닝/12] 이OO</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" s="9" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B4" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>91</v>
+      </c>
+      <c r="E4" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="F4" s="34"/>
+      <c r="G4" s="49" t="s">
+        <v>90</v>
+      </c>
+      <c r="H4" s="49"/>
+      <c r="I4" s="35" t="s">
+        <v>92</v>
+      </c>
+      <c r="J4" s="48" t="s">
+        <v>93</v>
+      </c>
+      <c r="K4" s="35"/>
+      <c r="L4" s="36" t="str">
+        <f>"["&amp;D4&amp;"/"&amp;G4&amp;"] "&amp;J4</f>
+        <v>[ENT/KJS] 이OO</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="38"/>
+      <c r="C5" s="38"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="39"/>
+      <c r="G5" s="39"/>
+      <c r="H5" s="39"/>
+      <c r="I5" s="39"/>
+      <c r="J5" s="39"/>
+      <c r="K5" s="39"/>
+      <c r="L5" s="40"/>
+    </row>
+    <row r="6" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
+      <c r="F6" s="37"/>
+      <c r="G6" s="37"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="37"/>
+      <c r="K6" s="37"/>
+      <c r="L6" s="37"/>
+    </row>
+    <row r="7" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B7" s="17"/>
+      <c r="C7" s="17"/>
+      <c r="D7" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E7" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F7" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="G7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="G2" s="7" t="s">
+      <c r="H7" s="18" t="s">
         <v>25</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I7" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="I2" s="22" t="s">
+      <c r="J7" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-    </row>
-    <row r="3" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="22"/>
-      <c r="B3" s="22"/>
-      <c r="C3" s="11">
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
+    </row>
+    <row r="8" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="17"/>
+      <c r="C8" s="17"/>
+      <c r="D8" s="20">
         <v>1311</v>
       </c>
-      <c r="D3" s="11">
+      <c r="E8" s="20">
         <v>12345678</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="F8" s="20" t="s">
         <v>40</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="G8" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="12" t="str">
+      <c r="H8" s="21" t="str">
         <f ca="1">TEXT(NOW(), "mmdd")</f>
         <v>0315</v>
       </c>
-      <c r="H3" s="13" t="str">
+      <c r="I8" s="22" t="str">
         <f ca="1">TEXT(NOW(), "hhmm")</f>
-        <v>0003</v>
-      </c>
-      <c r="I3" s="23" t="str">
-        <f ca="1">"["&amp;C3&amp;"]-["&amp;D3&amp;"]-["&amp;E3&amp;"]-["&amp;F3&amp;"]-["&amp;TEXT(G3,"0000")&amp;"]-["&amp;TEXT(H3,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003]</v>
-      </c>
-      <c r="J3" s="23"/>
-      <c r="K3" s="23"/>
-    </row>
-    <row r="4" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="7" t="s">
+        <v>0246</v>
+      </c>
+      <c r="J8" s="43" t="str">
+        <f ca="1">"["&amp;D8&amp;"]-["&amp;E8&amp;"]-["&amp;F8&amp;"]-["&amp;G8&amp;"]-["&amp;TEXT(H8,"0000")&amp;"]-["&amp;TEXT(I8,"0000")&amp;"]"</f>
+        <v>[1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246]</v>
+      </c>
+      <c r="K8" s="44"/>
+      <c r="L8" s="45"/>
+    </row>
+    <row r="9" spans="2:12" ht="33" x14ac:dyDescent="0.3">
+      <c r="B9" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="14" t="s">
+      <c r="C9" s="23" t="s">
         <v>64</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="D9" s="18" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="E9" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="F9" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="F4" s="7" t="s">
+      <c r="G9" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="H9" s="18" t="s">
         <v>4</v>
       </c>
-      <c r="H4" s="7" t="s">
+      <c r="I9" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="J9" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="J4" s="7" t="s">
+      <c r="K9" s="18" t="s">
         <v>33</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="L9" s="18" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+    <row r="10" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16">
-        <v>12</v>
-      </c>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="17"/>
-      <c r="H5" s="17"/>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="18" t="str">
-        <f ca="1">B5&amp;IF($I$3="","", "[A]"&amp;$I$3&amp;" / 지금:"&amp;D5&amp;" / 근거:"&amp;E5&amp;" / 요청:"&amp;F5&amp;" / "&amp;C5)</f>
-        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003] / 지금: / 근거: / 요청: / 12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="15" t="s">
+      <c r="C10" s="25"/>
+      <c r="D10" s="25">
+        <v>10</v>
+      </c>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
+      <c r="J10" s="18"/>
+      <c r="K10" s="18"/>
+      <c r="L10" s="26" t="str">
+        <f ca="1">C10&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / 지금:"&amp;E10&amp;" / 근거:"&amp;F10&amp;" / 요청:"&amp;G10&amp;" / "&amp;D10)</f>
+        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246] / 지금: / 근거: / 요청: / 10</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="24" t="s">
         <v>66</v>
       </c>
-      <c r="B6" s="17"/>
-      <c r="C6" s="17"/>
-      <c r="D6" s="19"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="18" t="str">
-        <f ca="1">IF($I$3="","", "[C]"&amp;$I$3&amp;" / "&amp;IF(G6="","{사유코드}",G6)&amp;" / 다음확인 "&amp;H6&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="15" t="s">
+      <c r="C11" s="18"/>
+      <c r="D11" s="18"/>
+      <c r="E11" s="18"/>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="46"/>
+      <c r="I11" s="25"/>
+      <c r="J11" s="18"/>
+      <c r="K11" s="18"/>
+      <c r="L11" s="26" t="str">
+        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H11="","{사유코드}",H11)&amp;" / 다음확인 "&amp;I11&amp;" (전화 1회 후)")</f>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="19"/>
-      <c r="E7" s="17"/>
-      <c r="F7" s="17"/>
-      <c r="G7" s="20"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="17"/>
-      <c r="J7" s="17"/>
-      <c r="K7" s="18" t="str">
-        <f ca="1">IF($I$3="","", "[C]"&amp;$I$3&amp;" / "&amp;IF(G7="","{사유코드}",G7)&amp;" / 다음확인 "&amp;H7&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="15" t="s">
+      <c r="C12" s="18"/>
+      <c r="D12" s="18"/>
+      <c r="E12" s="18"/>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="46"/>
+      <c r="I12" s="25"/>
+      <c r="J12" s="18"/>
+      <c r="K12" s="18"/>
+      <c r="L12" s="26" t="str">
+        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H12="","{사유코드}",H12)&amp;" / 다음확인 "&amp;I12&amp;" (전화 1회 후)")</f>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="16" t="s">
+      <c r="C13" s="18"/>
+      <c r="D13" s="18"/>
+      <c r="E13" s="25" t="s">
         <v>70</v>
       </c>
-      <c r="E8" s="17"/>
-      <c r="F8" s="17"/>
-      <c r="G8" s="17"/>
-      <c r="H8" s="17"/>
-      <c r="I8" s="16" t="s">
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
+      <c r="J13" s="25" t="s">
         <v>71</v>
       </c>
-      <c r="J8" s="16"/>
-      <c r="K8" s="18" t="str">
-        <f ca="1">IF($I$3="","", "[D]"&amp;$I$3&amp;" / 결과:"&amp;D8&amp;" / 현재:"&amp;I8&amp;" / F/U:"&amp;J8)</f>
-        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003] / 결과:확인 / 현재:처방확인 / F/U:</v>
-      </c>
-    </row>
-    <row r="9" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="15" t="s">
+      <c r="K13" s="25"/>
+      <c r="L13" s="26" t="str">
+        <f ca="1">IF($J$8="","", "[D]"&amp;$J$8&amp;" / 결과:"&amp;E13&amp;" / 현재:"&amp;J13&amp;" / F/U:"&amp;K13)</f>
+        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246] / 결과:확인 / 현재:처방확인 / F/U:</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="24" t="s">
         <v>34</v>
       </c>
-      <c r="B9" s="17"/>
-      <c r="C9" s="17"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="17"/>
-      <c r="F9" s="17"/>
-      <c r="G9" s="17"/>
-      <c r="H9" s="17"/>
-      <c r="I9" s="17"/>
-      <c r="J9" s="17"/>
-      <c r="K9" s="18" t="str">
-        <f ca="1">IF($I$3="","", "(보고)"&amp;$I$3&amp;"/"&amp;D9&amp;IF(D9="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003]/12</v>
-      </c>
-    </row>
-    <row r="10" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="7" t="s">
+      <c r="C14" s="18"/>
+      <c r="D14" s="18"/>
+      <c r="E14" s="46"/>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
+      <c r="J14" s="18"/>
+      <c r="K14" s="18"/>
+      <c r="L14" s="26" t="str">
+        <f ca="1">IF($J$8="","", "(보고)"&amp;$J$8&amp;"/"&amp;E14&amp;IF(E14="","","/")&amp;"12")</f>
+        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246]/12</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="B10" s="29" t="s">
+      <c r="C15" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="C10" s="29"/>
-      <c r="D10" s="22" t="s">
+      <c r="D15" s="27"/>
+      <c r="E15" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22" t="s">
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19" t="s">
         <v>76</v>
       </c>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="7"/>
-    </row>
-    <row r="11" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="15" t="s">
+      <c r="J15" s="19"/>
+      <c r="K15" s="19"/>
+      <c r="L15" s="18"/>
+    </row>
+    <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="32"/>
-      <c r="D11" s="30"/>
-      <c r="E11" s="30"/>
-      <c r="F11" s="30"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="30"/>
-      <c r="I11" s="30"/>
-      <c r="J11" s="30"/>
-      <c r="K11" s="18" t="str">
-        <f ca="1">IF($I$3="","", "[A][야간이음기록]"&amp;$I$3&amp;"/지금:"&amp;B11&amp;"/조치:"&amp;D11&amp;"/[D]"&amp;D11&amp;H11)</f>
-        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0003]/지금:/조치:/[D]</v>
-      </c>
-    </row>
-    <row r="12" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="9"/>
-      <c r="B12" s="8"/>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
-      <c r="I12" s="8"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="10"/>
-    </row>
-    <row r="13" spans="1:11" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="26" t="s">
+      <c r="C16" s="28"/>
+      <c r="D16" s="28"/>
+      <c r="E16" s="28"/>
+      <c r="F16" s="28"/>
+      <c r="G16" s="28"/>
+      <c r="H16" s="28"/>
+      <c r="I16" s="28"/>
+      <c r="J16" s="28"/>
+      <c r="K16" s="28"/>
+      <c r="L16" s="26" t="str">
+        <f ca="1">IF($J$8="","", "[A][야간이음기록]"&amp;$J$8&amp;"/지금:"&amp;C16&amp;"/조치:"&amp;E16&amp;"/[D]"&amp;E16&amp;I16)</f>
+        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246]/지금:/조치:/[D]</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="29"/>
+      <c r="C17" s="30"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
+      <c r="G17" s="30"/>
+      <c r="H17" s="30"/>
+      <c r="I17" s="30"/>
+      <c r="J17" s="30"/>
+      <c r="K17" s="30"/>
+      <c r="L17" s="31"/>
+    </row>
+    <row r="18" spans="2:12" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="32" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="27"/>
-      <c r="E13" s="27"/>
-      <c r="F13" s="27"/>
-      <c r="G13" s="27"/>
-      <c r="H13" s="27"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="27"/>
-      <c r="K13" s="28"/>
+      <c r="C18" s="32"/>
+      <c r="D18" s="32"/>
+      <c r="E18" s="32"/>
+      <c r="F18" s="32"/>
+      <c r="G18" s="32"/>
+      <c r="H18" s="32"/>
+      <c r="I18" s="32"/>
+      <c r="J18" s="32"/>
+      <c r="K18" s="32"/>
+      <c r="L18" s="32"/>
     </row>
   </sheetData>
-  <mergeCells count="12">
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="I3:K3"/>
-    <mergeCell ref="I2:K2"/>
-    <mergeCell ref="A1:K1"/>
-    <mergeCell ref="A13:K13"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="B10:C10"/>
-    <mergeCell ref="D10:G10"/>
-    <mergeCell ref="H10:J10"/>
-    <mergeCell ref="D11:G11"/>
-    <mergeCell ref="H11:J11"/>
-    <mergeCell ref="B11:C11"/>
+  <mergeCells count="15">
+    <mergeCell ref="B2:L2"/>
+    <mergeCell ref="B7:C8"/>
+    <mergeCell ref="B6:L6"/>
+    <mergeCell ref="J8:L8"/>
+    <mergeCell ref="J7:L7"/>
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B18:L18"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:H15"/>
+    <mergeCell ref="I15:K15"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="B5:C5">
+  <conditionalFormatting sqref="C10:D10">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>B5=12</formula>
+      <formula>C10=12</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>B5=4</formula>
+      <formula>C10=4</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>B5=10</formula>
+      <formula>C10=10</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>C5 C9</xm:sqref>
+          <xm:sqref>D10 D14</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$2:$B$14</xm:f>
           </x14:formula1>
-          <xm:sqref>G5 G8</xm:sqref>
+          <xm:sqref>H13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{72FFAC11-A338-427E-AF73-F7D83A85893C}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$J$2:$J$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D9</xm:sqref>
+          <xm:sqref>E14</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{54F24218-F1A5-4C39-A88F-EBBD79DE5CE8}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$L$2:$L$11</xm:f>
           </x14:formula1>
-          <xm:sqref>B5</xm:sqref>
+          <xm:sqref>C10</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{0D061B27-2ED0-4A89-8EF3-BCF08CD5E27F}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>G6</xm:sqref>
+          <xm:sqref>H11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{06472377-7060-4FB5-A3C2-0B85F9411171}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$D$2</xm:f>
           </x14:formula1>
-          <xm:sqref>G7</xm:sqref>
+          <xm:sqref>H12</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0BB3FC94-3ED2-4C84-A3ED-2F30071EDD5F}">
+          <x14:formula1>
+            <xm:f>'02_코드목록'!$B$23:$B$25</xm:f>
+          </x14:formula1>
+          <xm:sqref>F3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1371,7 +1821,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:M15"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="3" customWidth="1"/>
@@ -1420,11 +1870,11 @@
       <c r="D2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="33" t="s">
+      <c r="F2" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
+      <c r="G2" s="8"/>
+      <c r="H2" s="8"/>
       <c r="J2" s="5" t="s">
         <v>35</v>
       </c>
@@ -1443,9 +1893,9 @@
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="8"/>
       <c r="J3" s="5" t="s">
         <v>36</v>
       </c>
@@ -1464,9 +1914,9 @@
       <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
+      <c r="F4" s="8"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="8"/>
       <c r="J4" s="5" t="s">
         <v>37</v>
       </c>
@@ -1573,6 +2023,24 @@
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
         <v>65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A23" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="41" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B24" s="41" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B25" s="41" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/documents/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents/WeValue_현장ACD_메신저템플릿.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahee\Desktop\GitHub동기화폴더\2026-QI\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850E0E1A-E545-4AED-96A0-5C438052D32B}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C5DDA5-F958-4700-B2F1-23F796CFB5E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="소통메신저 양식 자동완성" sheetId="2" r:id="rId1"/>
-    <sheet name="02_코드목록" sheetId="3" r:id="rId2"/>
+    <sheet name="02_코드목록" sheetId="3" state="hidden" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -203,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="101">
   <si>
     <t>A(보고)</t>
   </si>
@@ -542,6 +542,33 @@
   </si>
   <si>
     <t>이OO</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>팀</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>A</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>B</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>C</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>E</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -849,7 +876,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -870,133 +897,160 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="11" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1338,7 +1392,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:L18"/>
+  <dimension ref="B1:L19"/>
   <sheetFormatPr defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.75" style="1" customWidth="1"/>
@@ -1358,111 +1412,111 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="42" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="10"/>
-      <c r="D1" s="11"/>
-      <c r="E1" s="11"/>
-      <c r="F1" s="11"/>
-      <c r="G1" s="11"/>
-      <c r="H1" s="11"/>
-      <c r="I1" s="11"/>
-      <c r="J1" s="11"/>
-      <c r="K1" s="11"/>
-      <c r="L1" s="11"/>
+      <c r="C1" s="42"/>
+      <c r="D1" s="43"/>
+      <c r="E1" s="43"/>
+      <c r="F1" s="43"/>
+      <c r="G1" s="43"/>
+      <c r="H1" s="43"/>
+      <c r="I1" s="43"/>
+      <c r="J1" s="43"/>
+      <c r="K1" s="43"/>
+      <c r="L1" s="43"/>
     </row>
     <row r="2" spans="2:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="12"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="12"/>
-      <c r="K2" s="12"/>
-      <c r="L2" s="12"/>
-    </row>
-    <row r="3" spans="2:12" s="9" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B3" s="13" t="s">
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+    </row>
+    <row r="3" spans="2:12" s="8" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B3" s="9" t="s">
         <v>80</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="9" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="14">
+      <c r="D3" s="10">
         <v>123</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="9" t="s">
         <v>78</v>
       </c>
-      <c r="F3" s="47" t="s">
+      <c r="F3" s="33" t="s">
         <v>87</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="9" t="s">
         <v>79</v>
       </c>
-      <c r="H3" s="14">
-        <v>12</v>
-      </c>
-      <c r="I3" s="15" t="s">
+      <c r="H3" s="33" t="s">
+        <v>95</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>92</v>
       </c>
-      <c r="J3" s="14" t="s">
+      <c r="J3" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="K3" s="15"/>
-      <c r="L3" s="16" t="str">
+      <c r="K3" s="11"/>
+      <c r="L3" s="12" t="str">
         <f>"["&amp;D3&amp;"/"&amp;F3&amp;"/"&amp;H3&amp;"] "&amp;J3</f>
-        <v>[123/이브닝/12] 이OO</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" s="9" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="33" t="s">
+        <v>[123/이브닝/A] 이OO</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" s="8" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B4" s="24" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="33" t="s">
+      <c r="C4" s="24" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="E4" s="34" t="s">
+      <c r="E4" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="34"/>
-      <c r="G4" s="49" t="s">
+      <c r="F4" s="47"/>
+      <c r="G4" s="48" t="s">
         <v>90</v>
       </c>
-      <c r="H4" s="49"/>
-      <c r="I4" s="35" t="s">
+      <c r="H4" s="48"/>
+      <c r="I4" s="25" t="s">
         <v>92</v>
       </c>
-      <c r="J4" s="48" t="s">
+      <c r="J4" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="K4" s="35"/>
-      <c r="L4" s="36" t="str">
+      <c r="K4" s="25"/>
+      <c r="L4" s="26" t="str">
         <f>"["&amp;D4&amp;"/"&amp;G4&amp;"] "&amp;J4</f>
         <v>[ENT/KJS] 이OO</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="38"/>
-      <c r="C5" s="38"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="39"/>
-      <c r="H5" s="39"/>
-      <c r="I5" s="39"/>
-      <c r="J5" s="39"/>
-      <c r="K5" s="39"/>
-      <c r="L5" s="40"/>
+      <c r="B5" s="27"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="28"/>
+      <c r="F5" s="28"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="28"/>
+      <c r="I5" s="28"/>
+      <c r="J5" s="28"/>
+      <c r="K5" s="28"/>
+      <c r="L5" s="29"/>
     </row>
     <row r="6" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="37" t="s">
@@ -1480,288 +1534,301 @@
       <c r="L6" s="37"/>
     </row>
     <row r="7" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="17"/>
-      <c r="C7" s="17"/>
-      <c r="D7" s="18" t="s">
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="18" t="s">
+      <c r="E7" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="18" t="s">
+      <c r="F7" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="18" t="s">
+      <c r="G7" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="18" t="s">
+      <c r="H7" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="18" t="s">
+      <c r="I7" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="41" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="19"/>
-      <c r="L7" s="19"/>
+      <c r="K7" s="41"/>
+      <c r="L7" s="41"/>
     </row>
     <row r="8" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="17"/>
-      <c r="C8" s="17"/>
-      <c r="D8" s="20">
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="14">
         <v>1311</v>
       </c>
-      <c r="E8" s="20">
+      <c r="E8" s="14">
         <v>12345678</v>
       </c>
-      <c r="F8" s="20" t="s">
+      <c r="F8" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="20" t="s">
+      <c r="G8" s="14" t="s">
         <v>72</v>
       </c>
-      <c r="H8" s="21" t="str">
+      <c r="H8" s="15" t="str">
         <f ca="1">TEXT(NOW(), "mmdd")</f>
         <v>0315</v>
       </c>
-      <c r="I8" s="22" t="str">
+      <c r="I8" s="16" t="str">
         <f ca="1">TEXT(NOW(), "hhmm")</f>
-        <v>0246</v>
-      </c>
-      <c r="J8" s="43" t="str">
+        <v>0310</v>
+      </c>
+      <c r="J8" s="38" t="str">
         <f ca="1">"["&amp;D8&amp;"]-["&amp;E8&amp;"]-["&amp;F8&amp;"]-["&amp;G8&amp;"]-["&amp;TEXT(H8,"0000")&amp;"]-["&amp;TEXT(I8,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246]</v>
-      </c>
-      <c r="K8" s="44"/>
-      <c r="L8" s="45"/>
-    </row>
-    <row r="9" spans="2:12" ht="33" x14ac:dyDescent="0.3">
-      <c r="B9" s="18" t="s">
+        <v>[1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310]</v>
+      </c>
+      <c r="K8" s="39"/>
+      <c r="L8" s="40"/>
+    </row>
+    <row r="9" spans="2:12" s="58" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="51"/>
+      <c r="C9" s="51"/>
+      <c r="D9" s="52"/>
+      <c r="E9" s="52"/>
+      <c r="F9" s="52"/>
+      <c r="G9" s="52"/>
+      <c r="H9" s="53"/>
+      <c r="I9" s="54"/>
+      <c r="J9" s="55"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="57"/>
+    </row>
+    <row r="10" spans="2:12" ht="33" x14ac:dyDescent="0.3">
+      <c r="B10" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C10" s="17" t="s">
         <v>64</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D10" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E10" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F10" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G10" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H10" s="13" t="s">
         <v>4</v>
       </c>
-      <c r="I9" s="18" t="s">
+      <c r="I10" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="J9" s="18" t="s">
+      <c r="J10" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="K9" s="18" t="s">
+      <c r="K10" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="L9" s="18" t="s">
+      <c r="L10" s="13" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="10" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="24" t="s">
+    <row r="11" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25">
+      <c r="C11" s="19"/>
+      <c r="D11" s="19">
         <v>10</v>
       </c>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="18"/>
-      <c r="L10" s="26" t="str">
-        <f ca="1">C10&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / 지금:"&amp;E10&amp;" / 근거:"&amp;F10&amp;" / 요청:"&amp;G10&amp;" / "&amp;D10)</f>
-        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246] / 지금: / 근거: / 요청: / 10</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="24" t="s">
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="20" t="str">
+        <f ca="1">C11&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / 지금:"&amp;E11&amp;" / 근거:"&amp;F11&amp;" / 요청:"&amp;G11&amp;" / "&amp;D11)</f>
+        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310] / 지금: / 근거: / 요청: / 10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="18" t="s">
         <v>66</v>
       </c>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="46"/>
-      <c r="I11" s="25"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="18"/>
-      <c r="L11" s="26" t="str">
-        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H11="","{사유코드}",H11)&amp;" / 다음확인 "&amp;I11&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="24" t="s">
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="13"/>
+      <c r="L12" s="20" t="str">
+        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H12="","{사유코드}",H12)&amp;" / 다음확인 "&amp;I12&amp;" (전화 1회 후)")</f>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="46"/>
-      <c r="I12" s="25"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="18"/>
-      <c r="L12" s="26" t="str">
-        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H12="","{사유코드}",H12)&amp;" / 다음확인 "&amp;I12&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="24" t="s">
+      <c r="C13" s="13"/>
+      <c r="D13" s="13"/>
+      <c r="E13" s="13"/>
+      <c r="F13" s="13"/>
+      <c r="G13" s="13"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="19"/>
+      <c r="J13" s="13"/>
+      <c r="K13" s="13"/>
+      <c r="L13" s="20" t="str">
+        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H13="","{사유코드}",H13)&amp;" / 다음확인 "&amp;I13&amp;" (전화 1회 후)")</f>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="18" t="s">
         <v>1</v>
       </c>
-      <c r="C13" s="18"/>
-      <c r="D13" s="18"/>
-      <c r="E13" s="25" t="s">
+      <c r="C14" s="13"/>
+      <c r="D14" s="13"/>
+      <c r="E14" s="19" t="s">
         <v>70</v>
       </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
-      <c r="J13" s="25" t="s">
+      <c r="F14" s="13"/>
+      <c r="G14" s="13"/>
+      <c r="H14" s="13"/>
+      <c r="I14" s="13"/>
+      <c r="J14" s="19" t="s">
         <v>71</v>
       </c>
-      <c r="K13" s="25"/>
-      <c r="L13" s="26" t="str">
-        <f ca="1">IF($J$8="","", "[D]"&amp;$J$8&amp;" / 결과:"&amp;E13&amp;" / 현재:"&amp;J13&amp;" / F/U:"&amp;K13)</f>
-        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246] / 결과:확인 / 현재:처방확인 / F/U:</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="C14" s="18"/>
-      <c r="D14" s="18"/>
-      <c r="E14" s="46"/>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="26" t="str">
-        <f ca="1">IF($J$8="","", "(보고)"&amp;$J$8&amp;"/"&amp;E14&amp;IF(E14="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246]/12</v>
+      <c r="K14" s="19"/>
+      <c r="L14" s="20" t="str">
+        <f ca="1">IF($J$8="","", "[D]"&amp;$J$8&amp;" / 결과:"&amp;E14&amp;" / 현재:"&amp;J14&amp;" / F/U:"&amp;K14)</f>
+        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310] / 결과:확인 / 현재:처방확인 / F/U:</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B15" s="18" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="13"/>
+      <c r="D15" s="13"/>
+      <c r="E15" s="32"/>
+      <c r="F15" s="13"/>
+      <c r="G15" s="13"/>
+      <c r="H15" s="13"/>
+      <c r="I15" s="13"/>
+      <c r="J15" s="13"/>
+      <c r="K15" s="13"/>
+      <c r="L15" s="20" t="str">
+        <f ca="1">IF($J$8="","", "(보고)"&amp;$J$8&amp;"/"&amp;E15&amp;IF(E15="","","/")&amp;"12")</f>
+        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310]/12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C16" s="45" t="s">
         <v>74</v>
       </c>
-      <c r="D15" s="27"/>
-      <c r="E15" s="19" t="s">
+      <c r="D16" s="45"/>
+      <c r="E16" s="41" t="s">
         <v>75</v>
       </c>
-      <c r="F15" s="19"/>
-      <c r="G15" s="19"/>
-      <c r="H15" s="19"/>
-      <c r="I15" s="19" t="s">
+      <c r="F16" s="41"/>
+      <c r="G16" s="41"/>
+      <c r="H16" s="41"/>
+      <c r="I16" s="41" t="s">
         <v>76</v>
       </c>
-      <c r="J15" s="19"/>
-      <c r="K15" s="19"/>
-      <c r="L15" s="18"/>
-    </row>
-    <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="24" t="s">
+      <c r="J16" s="41"/>
+      <c r="K16" s="41"/>
+      <c r="L16" s="13"/>
+    </row>
+    <row r="17" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
-      <c r="K16" s="28"/>
-      <c r="L16" s="26" t="str">
-        <f ca="1">IF($J$8="","", "[A][야간이음기록]"&amp;$J$8&amp;"/지금:"&amp;C16&amp;"/조치:"&amp;E16&amp;"/[D]"&amp;E16&amp;I16)</f>
-        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0246]/지금:/조치:/[D]</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="29"/>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="30"/>
-      <c r="L17" s="31"/>
-    </row>
-    <row r="18" spans="2:12" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="32" t="s">
+      <c r="C17" s="46"/>
+      <c r="D17" s="46"/>
+      <c r="E17" s="46"/>
+      <c r="F17" s="46"/>
+      <c r="G17" s="46"/>
+      <c r="H17" s="46"/>
+      <c r="I17" s="46"/>
+      <c r="J17" s="46"/>
+      <c r="K17" s="46"/>
+      <c r="L17" s="20" t="str">
+        <f ca="1">IF($J$8="","", "[A][야간이음기록]"&amp;$J$8&amp;"/지금:"&amp;C17&amp;"/조치:"&amp;E17&amp;"/[D]"&amp;E17&amp;I17)</f>
+        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310]/지금:/조치:/[D]</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="21"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="22"/>
+      <c r="E18" s="22"/>
+      <c r="F18" s="22"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="22"/>
+      <c r="I18" s="22"/>
+      <c r="J18" s="22"/>
+      <c r="K18" s="22"/>
+      <c r="L18" s="23"/>
+    </row>
+    <row r="19" spans="2:12" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="44" t="s">
         <v>39</v>
       </c>
-      <c r="C18" s="32"/>
-      <c r="D18" s="32"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="32"/>
-      <c r="G18" s="32"/>
-      <c r="H18" s="32"/>
-      <c r="I18" s="32"/>
-      <c r="J18" s="32"/>
-      <c r="K18" s="32"/>
-      <c r="L18" s="32"/>
+      <c r="C19" s="44"/>
+      <c r="D19" s="44"/>
+      <c r="E19" s="44"/>
+      <c r="F19" s="44"/>
+      <c r="G19" s="44"/>
+      <c r="H19" s="44"/>
+      <c r="I19" s="44"/>
+      <c r="J19" s="44"/>
+      <c r="K19" s="44"/>
+      <c r="L19" s="44"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="B1:L1"/>
+    <mergeCell ref="B19:L19"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="E16:H16"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="E17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
     <mergeCell ref="B2:L2"/>
     <mergeCell ref="B7:C8"/>
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="J8:L8"/>
     <mergeCell ref="J7:L7"/>
-    <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B18:L18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:H15"/>
-    <mergeCell ref="I15:K15"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="C10:D10">
+  <conditionalFormatting sqref="C11:D11">
     <cfRule type="expression" dxfId="2" priority="1">
-      <formula>C10=12</formula>
+      <formula>C11=12</formula>
     </cfRule>
     <cfRule type="expression" dxfId="1" priority="2">
-      <formula>C10=4</formula>
+      <formula>C11=4</formula>
     </cfRule>
     <cfRule type="expression" dxfId="0" priority="3">
-      <formula>C10=10</formula>
+      <formula>C11=10</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1769,48 +1836,54 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D10 D14</xm:sqref>
+          <xm:sqref>D11 D15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$2:$B$14</xm:f>
           </x14:formula1>
-          <xm:sqref>H13</xm:sqref>
+          <xm:sqref>H14</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{72FFAC11-A338-427E-AF73-F7D83A85893C}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$J$2:$J$4</xm:f>
           </x14:formula1>
-          <xm:sqref>E14</xm:sqref>
+          <xm:sqref>E15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{54F24218-F1A5-4C39-A88F-EBBD79DE5CE8}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$L$2:$L$11</xm:f>
           </x14:formula1>
-          <xm:sqref>C10</xm:sqref>
+          <xm:sqref>C11</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{0D061B27-2ED0-4A89-8EF3-BCF08CD5E27F}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>H11</xm:sqref>
+          <xm:sqref>H12</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{06472377-7060-4FB5-A3C2-0B85F9411171}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$D$2</xm:f>
           </x14:formula1>
-          <xm:sqref>H12</xm:sqref>
+          <xm:sqref>H13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0BB3FC94-3ED2-4C84-A3ED-2F30071EDD5F}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$23:$B$25</xm:f>
           </x14:formula1>
           <xm:sqref>F3</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{520AB831-8948-4772-A944-BFC6D5A572B3}">
+          <x14:formula1>
+            <xm:f>'02_코드목록'!$E$23:$E$27</xm:f>
+          </x14:formula1>
+          <xm:sqref>H3</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1821,7 +1894,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="3" customWidth="1"/>
@@ -1870,11 +1943,11 @@
       <c r="D2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="7" t="s">
+      <c r="F2" s="49" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="8"/>
-      <c r="H2" s="8"/>
+      <c r="G2" s="50"/>
+      <c r="H2" s="50"/>
       <c r="J2" s="5" t="s">
         <v>35</v>
       </c>
@@ -1893,9 +1966,9 @@
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="8"/>
+      <c r="F3" s="50"/>
+      <c r="G3" s="50"/>
+      <c r="H3" s="50"/>
       <c r="J3" s="5" t="s">
         <v>36</v>
       </c>
@@ -1914,9 +1987,9 @@
       <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="8"/>
+      <c r="F4" s="50"/>
+      <c r="G4" s="50"/>
+      <c r="H4" s="50"/>
       <c r="J4" s="5" t="s">
         <v>37</v>
       </c>
@@ -2025,22 +2098,44 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A23" s="42" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="B23" s="41" t="s">
+      <c r="B23" s="30" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B24" s="41" t="s">
+      <c r="D23" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B24" s="30" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="B25" s="41" t="s">
+      <c r="E24" s="7" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B25" s="30" t="s">
         <v>89</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E26" s="7" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="E27" s="7" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/documents/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents/WeValue_현장ACD_메신저템플릿.xlsx
@@ -8,13 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahee\Desktop\GitHub동기화폴더\2026-QI\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66C5DDA5-F958-4700-B2F1-23F796CFB5E0}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF65B98D-1107-4F62-8BFD-FA91B1AFCA67}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="소통메신저 양식 자동완성" sheetId="2" r:id="rId1"/>
-    <sheet name="02_코드목록" sheetId="3" state="hidden" r:id="rId2"/>
+    <sheet name="02_코드목록" sheetId="3" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
 </workbook>
@@ -203,7 +203,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="108">
   <si>
     <t>A(보고)</t>
   </si>
@@ -450,10 +450,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>확인</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>처방확인</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -519,9 +515,6 @@
   </si>
   <si>
     <t>이브닝</t>
-  </si>
-  <si>
-    <t>이브닝</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -533,10 +526,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>ENT</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>이름</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -550,9 +539,6 @@
   </si>
   <si>
     <t>A</t>
-  </si>
-  <si>
-    <t>A</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -570,6 +556,47 @@
   <si>
     <t>E</t>
     <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>141-MH</t>
+  </si>
+  <si>
+    <t>141-MH</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>142-MH</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>131-ENT</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>131-URO</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>92-MC</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>92-CS</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA 소속과</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>병동소속</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>나이트</t>
+  </si>
+  <si>
+    <t>B</t>
   </si>
 </sst>
 </file>
@@ -655,14 +682,6 @@
       <charset val="129"/>
     </font>
     <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="24"/>
       <name val="맑은 고딕"/>
@@ -691,6 +710,14 @@
       <name val="돋움"/>
       <family val="3"/>
       <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="9">
@@ -735,12 +762,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.59999389629810485"/>
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -854,9 +881,16 @@
       <top style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </top>
-      <bottom style="thin">
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color theme="0" tint="-0.249977111117893"/>
-      </bottom>
+      </top>
+      <bottom/>
       <diagonal/>
     </border>
     <border>
@@ -867,8 +901,17 @@
       <top style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
       <bottom style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -876,7 +919,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -899,36 +942,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -947,15 +963,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -971,86 +978,128 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="11" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1412,394 +1461,392 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="42" t="s">
+      <c r="B1" s="23" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="42"/>
-      <c r="D1" s="43"/>
-      <c r="E1" s="43"/>
-      <c r="F1" s="43"/>
-      <c r="G1" s="43"/>
-      <c r="H1" s="43"/>
-      <c r="I1" s="43"/>
-      <c r="J1" s="43"/>
-      <c r="K1" s="43"/>
-      <c r="L1" s="43"/>
-    </row>
-    <row r="2" spans="2:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="35" t="s">
+      <c r="C1" s="23"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+    </row>
+    <row r="2" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B2" s="29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="29"/>
+      <c r="G2" s="29"/>
+      <c r="H2" s="29"/>
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="29"/>
+    </row>
+    <row r="3" spans="2:12" s="37" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="D3" s="59">
+        <v>92</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F3" s="59" t="s">
+        <v>106</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="59" t="s">
+        <v>107</v>
+      </c>
+      <c r="I3" s="35" t="s">
+        <v>89</v>
+      </c>
+      <c r="J3" s="34" t="s">
+        <v>90</v>
+      </c>
+      <c r="K3" s="35"/>
+      <c r="L3" s="36" t="str">
+        <f>"["&amp;D3&amp;"/"&amp;F3&amp;"/"&amp;H3&amp;"] "&amp;J3</f>
+        <v>[92/나이트/B] 이OO</v>
+      </c>
+    </row>
+    <row r="4" spans="2:12" s="37" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="38" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="D4" s="58" t="s">
+        <v>97</v>
+      </c>
+      <c r="E4" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="F4" s="40"/>
+      <c r="G4" s="41" t="s">
+        <v>88</v>
+      </c>
+      <c r="H4" s="41"/>
+      <c r="I4" s="42" t="s">
+        <v>89</v>
+      </c>
+      <c r="J4" s="39" t="s">
+        <v>90</v>
+      </c>
+      <c r="K4" s="42"/>
+      <c r="L4" s="43" t="str">
+        <f>"["&amp;D4&amp;"/"&amp;G4&amp;"] "&amp;J4</f>
+        <v>[141-MH/KJS] 이OO</v>
+      </c>
+    </row>
+    <row r="5" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
+      <c r="J5" s="16"/>
+      <c r="K5" s="16"/>
+      <c r="L5" s="17"/>
+    </row>
+    <row r="6" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B6" s="31" t="s">
         <v>84</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="35"/>
-      <c r="G2" s="35"/>
-      <c r="H2" s="35"/>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="35"/>
-    </row>
-    <row r="3" spans="2:12" s="8" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B3" s="9" t="s">
-        <v>80</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="10">
-        <v>123</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>78</v>
-      </c>
-      <c r="F3" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>79</v>
-      </c>
-      <c r="H3" s="33" t="s">
-        <v>95</v>
-      </c>
-      <c r="I3" s="11" t="s">
-        <v>92</v>
-      </c>
-      <c r="J3" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="K3" s="11"/>
-      <c r="L3" s="12" t="str">
-        <f>"["&amp;D3&amp;"/"&amp;F3&amp;"/"&amp;H3&amp;"] "&amp;J3</f>
-        <v>[123/이브닝/A] 이OO</v>
-      </c>
-    </row>
-    <row r="4" spans="2:12" s="8" customFormat="1" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B4" s="24" t="s">
-        <v>81</v>
-      </c>
-      <c r="C4" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="E4" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="F4" s="47"/>
-      <c r="G4" s="48" t="s">
-        <v>90</v>
-      </c>
-      <c r="H4" s="48"/>
-      <c r="I4" s="25" t="s">
-        <v>92</v>
-      </c>
-      <c r="J4" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="K4" s="25"/>
-      <c r="L4" s="26" t="str">
-        <f>"["&amp;D4&amp;"/"&amp;G4&amp;"] "&amp;J4</f>
-        <v>[ENT/KJS] 이OO</v>
-      </c>
-    </row>
-    <row r="5" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="27"/>
-      <c r="C5" s="27"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="28"/>
-      <c r="I5" s="28"/>
-      <c r="J5" s="28"/>
-      <c r="K5" s="28"/>
-      <c r="L5" s="29"/>
-    </row>
-    <row r="6" spans="2:12" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="37" t="s">
-        <v>85</v>
-      </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
-      <c r="F6" s="37"/>
-      <c r="G6" s="37"/>
-      <c r="H6" s="37"/>
-      <c r="I6" s="37"/>
-      <c r="J6" s="37"/>
-      <c r="K6" s="37"/>
-      <c r="L6" s="37"/>
+      <c r="C6" s="31"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="31"/>
+      <c r="H6" s="31"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="31"/>
+      <c r="L6" s="31"/>
     </row>
     <row r="7" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="13" t="s">
+      <c r="B7" s="30"/>
+      <c r="C7" s="30"/>
+      <c r="D7" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="13" t="s">
+      <c r="E7" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="13" t="s">
+      <c r="G7" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="8" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="13" t="s">
+      <c r="I7" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="41" t="s">
+      <c r="J7" s="27" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="41"/>
-      <c r="L7" s="41"/>
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
     </row>
     <row r="8" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="14">
+      <c r="B8" s="46"/>
+      <c r="C8" s="46"/>
+      <c r="D8" s="47">
         <v>1311</v>
       </c>
-      <c r="E8" s="14">
+      <c r="E8" s="47">
         <v>12345678</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="47" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="14" t="s">
-        <v>72</v>
-      </c>
-      <c r="H8" s="15" t="str">
+      <c r="G8" s="47" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="48" t="str">
         <f ca="1">TEXT(NOW(), "mmdd")</f>
         <v>0315</v>
       </c>
-      <c r="I8" s="16" t="str">
+      <c r="I8" s="49" t="str">
         <f ca="1">TEXT(NOW(), "hhmm")</f>
-        <v>0310</v>
-      </c>
-      <c r="J8" s="38" t="str">
+        <v>1704</v>
+      </c>
+      <c r="J8" s="50" t="str">
         <f ca="1">"["&amp;D8&amp;"]-["&amp;E8&amp;"]-["&amp;F8&amp;"]-["&amp;G8&amp;"]-["&amp;TEXT(H8,"0000")&amp;"]-["&amp;TEXT(I8,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310]</v>
-      </c>
-      <c r="K8" s="39"/>
-      <c r="L8" s="40"/>
-    </row>
-    <row r="9" spans="2:12" s="58" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="51"/>
-      <c r="C9" s="51"/>
-      <c r="D9" s="52"/>
-      <c r="E9" s="52"/>
-      <c r="F9" s="52"/>
-      <c r="G9" s="52"/>
-      <c r="H9" s="53"/>
-      <c r="I9" s="54"/>
-      <c r="J9" s="55"/>
-      <c r="K9" s="56"/>
-      <c r="L9" s="57"/>
+        <v>[1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704]</v>
+      </c>
+      <c r="K8" s="51"/>
+      <c r="L8" s="52"/>
+    </row>
+    <row r="9" spans="2:12" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="54"/>
+      <c r="E9" s="54"/>
+      <c r="F9" s="54"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="54"/>
+      <c r="K9" s="54"/>
+      <c r="L9" s="54"/>
     </row>
     <row r="10" spans="2:12" ht="33" x14ac:dyDescent="0.3">
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="17" t="s">
+      <c r="C10" s="45" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="13" t="s">
+      <c r="D10" s="44" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="13" t="s">
+      <c r="E10" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="13" t="s">
+      <c r="F10" s="44" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="13" t="s">
+      <c r="G10" s="44" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="44" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="13" t="s">
+      <c r="I10" s="44" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="13" t="s">
+      <c r="J10" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="13" t="s">
+      <c r="K10" s="44" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="13" t="s">
+      <c r="L10" s="44" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="18" t="s">
+      <c r="B11" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="19"/>
-      <c r="D11" s="19">
+      <c r="C11" s="10"/>
+      <c r="D11" s="10">
         <v>10</v>
       </c>
-      <c r="E11" s="19"/>
-      <c r="F11" s="19"/>
-      <c r="G11" s="19"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
-      <c r="J11" s="13"/>
-      <c r="K11" s="13"/>
-      <c r="L11" s="20" t="str">
+      <c r="E11" s="10"/>
+      <c r="F11" s="10"/>
+      <c r="G11" s="10"/>
+      <c r="H11" s="8"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="8"/>
+      <c r="K11" s="8"/>
+      <c r="L11" s="11" t="str">
         <f ca="1">C11&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / 지금:"&amp;E11&amp;" / 근거:"&amp;F11&amp;" / 요청:"&amp;G11&amp;" / "&amp;D11)</f>
-        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310] / 지금: / 근거: / 요청: / 10</v>
+        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704] / 지금: / 근거: / 요청: / 10</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="18" t="s">
+      <c r="B12" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="13"/>
-      <c r="D12" s="13"/>
-      <c r="E12" s="13"/>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="19"/>
-      <c r="J12" s="13"/>
-      <c r="K12" s="13"/>
-      <c r="L12" s="20" t="str">
+      <c r="C12" s="8"/>
+      <c r="D12" s="8"/>
+      <c r="E12" s="8"/>
+      <c r="F12" s="8"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="60"/>
+      <c r="I12" s="10"/>
+      <c r="J12" s="8"/>
+      <c r="K12" s="8"/>
+      <c r="L12" s="11" t="str">
         <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H12="","{사유코드}",H12)&amp;" / 다음확인 "&amp;I12&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="18" t="s">
+      <c r="B13" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="19"/>
-      <c r="J13" s="13"/>
-      <c r="K13" s="13"/>
-      <c r="L13" s="20" t="str">
+      <c r="C13" s="8"/>
+      <c r="D13" s="8"/>
+      <c r="E13" s="8"/>
+      <c r="F13" s="8"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="60"/>
+      <c r="I13" s="10"/>
+      <c r="J13" s="8"/>
+      <c r="K13" s="8"/>
+      <c r="L13" s="11" t="str">
         <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H13="","{사유코드}",H13)&amp;" / 다음확인 "&amp;I13&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="18" t="s">
+      <c r="B14" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="13"/>
-      <c r="D14" s="13"/>
-      <c r="E14" s="19" t="s">
+      <c r="C14" s="8"/>
+      <c r="D14" s="8"/>
+      <c r="E14" s="10"/>
+      <c r="F14" s="8"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="8"/>
+      <c r="I14" s="8"/>
+      <c r="J14" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
-      <c r="J14" s="19" t="s">
-        <v>71</v>
-      </c>
-      <c r="K14" s="19"/>
-      <c r="L14" s="20" t="str">
+      <c r="K14" s="10"/>
+      <c r="L14" s="11" t="str">
         <f ca="1">IF($J$8="","", "[D]"&amp;$J$8&amp;" / 결과:"&amp;E14&amp;" / 현재:"&amp;J14&amp;" / F/U:"&amp;K14)</f>
-        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310] / 결과:확인 / 현재:처방확인 / F/U:</v>
+        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704] / 결과: / 현재:처방확인 / F/U:</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="18" t="s">
+      <c r="B15" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="13"/>
-      <c r="D15" s="13"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
-      <c r="J15" s="13"/>
-      <c r="K15" s="13"/>
-      <c r="L15" s="20" t="str">
+      <c r="C15" s="8"/>
+      <c r="D15" s="8"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="8"/>
+      <c r="G15" s="8"/>
+      <c r="H15" s="8"/>
+      <c r="I15" s="8"/>
+      <c r="J15" s="8"/>
+      <c r="K15" s="8"/>
+      <c r="L15" s="11" t="str">
         <f ca="1">IF($J$8="","", "(보고)"&amp;$J$8&amp;"/"&amp;E15&amp;IF(E15="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310]/12</v>
+        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704]/12</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="13" t="s">
+      <c r="B16" s="8" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="45" t="s">
+      <c r="C16" s="26" t="s">
+        <v>73</v>
+      </c>
+      <c r="D16" s="26"/>
+      <c r="E16" s="27" t="s">
         <v>74</v>
       </c>
-      <c r="D16" s="45"/>
-      <c r="E16" s="41" t="s">
+      <c r="F16" s="27"/>
+      <c r="G16" s="27"/>
+      <c r="H16" s="27"/>
+      <c r="I16" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="F16" s="41"/>
-      <c r="G16" s="41"/>
-      <c r="H16" s="41"/>
-      <c r="I16" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="J16" s="41"/>
-      <c r="K16" s="41"/>
-      <c r="L16" s="13"/>
+      <c r="J16" s="27"/>
+      <c r="K16" s="27"/>
+      <c r="L16" s="8"/>
     </row>
     <row r="17" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="C17" s="46"/>
-      <c r="D17" s="46"/>
-      <c r="E17" s="46"/>
-      <c r="F17" s="46"/>
-      <c r="G17" s="46"/>
-      <c r="H17" s="46"/>
-      <c r="I17" s="46"/>
-      <c r="J17" s="46"/>
-      <c r="K17" s="46"/>
-      <c r="L17" s="20" t="str">
+      <c r="B17" s="9" t="s">
+        <v>72</v>
+      </c>
+      <c r="C17" s="28"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="28"/>
+      <c r="F17" s="28"/>
+      <c r="G17" s="28"/>
+      <c r="H17" s="28"/>
+      <c r="I17" s="28"/>
+      <c r="J17" s="28"/>
+      <c r="K17" s="28"/>
+      <c r="L17" s="11" t="str">
         <f ca="1">IF($J$8="","", "[A][야간이음기록]"&amp;$J$8&amp;"/지금:"&amp;C17&amp;"/조치:"&amp;E17&amp;"/[D]"&amp;E17&amp;I17)</f>
-        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0315]-[0310]/지금:/조치:/[D]</v>
+        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704]/지금:/조치:/[D]</v>
       </c>
     </row>
     <row r="18" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="21"/>
-      <c r="C18" s="22"/>
-      <c r="D18" s="22"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="23"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="13"/>
+      <c r="F18" s="13"/>
+      <c r="G18" s="13"/>
+      <c r="H18" s="13"/>
+      <c r="I18" s="13"/>
+      <c r="J18" s="13"/>
+      <c r="K18" s="13"/>
+      <c r="L18" s="14"/>
     </row>
     <row r="19" spans="2:12" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="44" t="s">
+      <c r="B19" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="44"/>
-      <c r="D19" s="44"/>
-      <c r="E19" s="44"/>
-      <c r="F19" s="44"/>
-      <c r="G19" s="44"/>
-      <c r="H19" s="44"/>
-      <c r="I19" s="44"/>
-      <c r="J19" s="44"/>
-      <c r="K19" s="44"/>
-      <c r="L19" s="44"/>
+      <c r="C19" s="25"/>
+      <c r="D19" s="25"/>
+      <c r="E19" s="25"/>
+      <c r="F19" s="25"/>
+      <c r="G19" s="25"/>
+      <c r="H19" s="25"/>
+      <c r="I19" s="25"/>
+      <c r="J19" s="25"/>
+      <c r="K19" s="25"/>
+      <c r="L19" s="25"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1836,7 +1883,7 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="8">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="10">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$A$2:$A$4</xm:f>
@@ -1885,6 +1932,18 @@
           </x14:formula1>
           <xm:sqref>H3</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F832BF57-460C-4480-8BA8-EBC99E7230DB}">
+          <x14:formula1>
+            <xm:f>'02_코드목록'!$K$23:$K$26</xm:f>
+          </x14:formula1>
+          <xm:sqref>D3</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{33E7ADC8-529F-4927-AAE9-C790AFD91F36}">
+          <x14:formula1>
+            <xm:f>'02_코드목록'!$H$23:$H$28</xm:f>
+          </x14:formula1>
+          <xm:sqref>D4</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -1894,7 +1953,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:M28"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="3" customWidth="1"/>
@@ -1943,11 +2002,11 @@
       <c r="D2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="49" t="s">
+      <c r="F2" s="32" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="50"/>
-      <c r="H2" s="50"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="33"/>
       <c r="J2" s="5" t="s">
         <v>35</v>
       </c>
@@ -1966,9 +2025,9 @@
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="50"/>
-      <c r="G3" s="50"/>
-      <c r="H3" s="50"/>
+      <c r="F3" s="33"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="33"/>
       <c r="J3" s="5" t="s">
         <v>36</v>
       </c>
@@ -1987,9 +2046,9 @@
       <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="50"/>
-      <c r="G4" s="50"/>
-      <c r="H4" s="50"/>
+      <c r="F4" s="33"/>
+      <c r="G4" s="33"/>
+      <c r="H4" s="33"/>
       <c r="J4" s="5" t="s">
         <v>37</v>
       </c>
@@ -2098,44 +2157,82 @@
         <v>65</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="31" t="s">
-        <v>78</v>
-      </c>
-      <c r="B23" s="30" t="s">
+    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A23" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="B23" s="18" t="s">
+        <v>85</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="G23" s="21" t="s">
+        <v>104</v>
+      </c>
+      <c r="H23" s="21" t="s">
+        <v>103</v>
+      </c>
+      <c r="J23" s="21" t="s">
+        <v>105</v>
+      </c>
+      <c r="K23" s="21">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B24" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="D23" s="7" t="s">
+      <c r="E24" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>102</v>
+      </c>
+      <c r="K24" s="21">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="18" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="E23" s="7" t="s">
+      <c r="H25" s="57" t="s">
+        <v>101</v>
+      </c>
+      <c r="K25" s="21">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E26" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="H26" s="21" t="s">
+        <v>100</v>
+      </c>
+      <c r="K26" s="21">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E27" s="7" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B24" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B25" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="E25" s="7" t="s">
+      <c r="H27" s="21" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E26" s="7" t="s">
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H28" s="21" t="s">
         <v>99</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="E27" s="7" t="s">
-        <v>100</v>
       </c>
     </row>
   </sheetData>

--- a/documents/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents/WeValue_현장ACD_메신저템플릿.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahee\Desktop\GitHub동기화폴더\2026-QI\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF65B98D-1107-4F62-8BFD-FA91B1AFCA67}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFFAFA4-7CD9-4F9C-BC7E-7108EF172574}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -59,27 +59,6 @@
             <charset val="129"/>
           </rPr>
           <t>셀은</t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="돋움"/>
-            <family val="3"/>
-            <charset val="129"/>
-          </rPr>
-          <t>모두</t>
         </r>
         <r>
           <rPr>
@@ -506,10 +485,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>CaseId</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>데이</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -597,6 +572,10 @@
   </si>
   <si>
     <t>B</t>
+  </si>
+  <si>
+    <t>CASE ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -767,7 +746,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -792,19 +771,6 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color theme="0" tint="-0.249977111117893"/>
       </left>
       <right style="thin">
@@ -820,98 +786,38 @@
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0" tint="-0.14999847407452621"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
-        <color theme="0" tint="-0.499984740745262"/>
+        <color theme="0" tint="-0.14999847407452621"/>
       </right>
-      <top/>
-      <bottom/>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
+        <color theme="0" tint="-0.14999847407452621"/>
       </left>
       <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
+        <color theme="0" tint="-0.14999847407452621"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
+        <color theme="0" tint="-0.14999847407452621"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
+      <top/>
       <bottom style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </right>
-      <top style="thin">
-        <color theme="0" tint="-0.249977111117893"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
+        <color theme="0" tint="-0.14999847407452621"/>
       </bottom>
       <diagonal/>
     </border>
@@ -919,7 +825,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -942,9 +848,102 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -954,152 +953,26 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="7" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="12" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="7" borderId="12" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1460,393 +1333,381 @@
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="23" t="s">
+    <row r="1" spans="2:12" s="8" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="48" t="s">
         <v>41</v>
       </c>
-      <c r="C1" s="23"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
+      <c r="I1" s="49"/>
+      <c r="J1" s="49"/>
+      <c r="K1" s="49"/>
+      <c r="L1" s="49"/>
     </row>
     <row r="2" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="47" t="s">
         <v>83</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="29"/>
-      <c r="G2" s="29"/>
-      <c r="H2" s="29"/>
-      <c r="I2" s="29"/>
-      <c r="J2" s="29"/>
-      <c r="K2" s="29"/>
-      <c r="L2" s="29"/>
-    </row>
-    <row r="3" spans="2:12" s="37" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="20" t="s">
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="47"/>
+      <c r="K2" s="47"/>
+      <c r="L2" s="47"/>
+    </row>
+    <row r="3" spans="2:12" s="13" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="59">
+      <c r="D3" s="19">
         <v>92</v>
       </c>
-      <c r="E3" s="20" t="s">
+      <c r="E3" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="59" t="s">
+      <c r="F3" s="19" t="s">
+        <v>105</v>
+      </c>
+      <c r="G3" s="18" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="G3" s="20" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="59" t="s">
-        <v>107</v>
-      </c>
-      <c r="I3" s="35" t="s">
+      <c r="I3" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="J3" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="J3" s="34" t="s">
-        <v>90</v>
-      </c>
-      <c r="K3" s="35"/>
-      <c r="L3" s="36" t="str">
+      <c r="K3" s="20"/>
+      <c r="L3" s="22" t="str">
         <f>"["&amp;D3&amp;"/"&amp;F3&amp;"/"&amp;H3&amp;"] "&amp;J3</f>
         <v>[92/나이트/B] 이OO</v>
       </c>
     </row>
-    <row r="4" spans="2:12" s="37" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="38" t="s">
+    <row r="4" spans="2:12" s="13" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="18" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="38" t="s">
+      <c r="C4" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="58" t="s">
-        <v>97</v>
-      </c>
-      <c r="E4" s="40" t="s">
+      <c r="D4" s="19" t="s">
+        <v>96</v>
+      </c>
+      <c r="E4" s="23" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="40"/>
-      <c r="G4" s="41" t="s">
+      <c r="F4" s="23"/>
+      <c r="G4" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="24"/>
+      <c r="I4" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="H4" s="41"/>
-      <c r="I4" s="42" t="s">
+      <c r="J4" s="21" t="s">
         <v>89</v>
       </c>
-      <c r="J4" s="39" t="s">
-        <v>90</v>
-      </c>
-      <c r="K4" s="42"/>
-      <c r="L4" s="43" t="str">
+      <c r="K4" s="20"/>
+      <c r="L4" s="22" t="str">
         <f>"["&amp;D4&amp;"/"&amp;G4&amp;"] "&amp;J4</f>
         <v>[141-MH/KJS] 이OO</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="15"/>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="16"/>
-      <c r="J5" s="16"/>
-      <c r="K5" s="16"/>
-      <c r="L5" s="17"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="26"/>
+      <c r="H5" s="26"/>
+      <c r="I5" s="26"/>
+      <c r="J5" s="26"/>
+      <c r="K5" s="26"/>
+      <c r="L5" s="27"/>
     </row>
     <row r="6" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="31" t="s">
-        <v>84</v>
-      </c>
-      <c r="C6" s="31"/>
-      <c r="D6" s="31"/>
-      <c r="E6" s="31"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="31"/>
-      <c r="H6" s="31"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="31"/>
-      <c r="L6" s="31"/>
+      <c r="B6" s="17" t="s">
+        <v>107</v>
+      </c>
+      <c r="C6" s="17"/>
+      <c r="D6" s="17"/>
+      <c r="E6" s="17"/>
+      <c r="F6" s="17"/>
+      <c r="G6" s="17"/>
+      <c r="H6" s="17"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="17"/>
     </row>
     <row r="7" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="30"/>
-      <c r="C7" s="30"/>
-      <c r="D7" s="8" t="s">
+      <c r="B7" s="28"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="8" t="s">
+      <c r="E7" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="8" t="s">
+      <c r="F7" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="8" t="s">
+      <c r="G7" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="H7" s="29" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="I7" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="27" t="s">
+      <c r="J7" s="30" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
+      <c r="K7" s="30"/>
+      <c r="L7" s="30"/>
     </row>
     <row r="8" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="46"/>
-      <c r="C8" s="46"/>
-      <c r="D8" s="47">
+      <c r="B8" s="28"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="31">
         <v>1311</v>
       </c>
-      <c r="E8" s="47">
+      <c r="E8" s="31">
         <v>12345678</v>
       </c>
-      <c r="F8" s="47" t="s">
+      <c r="F8" s="31" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="47" t="s">
+      <c r="G8" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="48" t="str">
+      <c r="H8" s="32" t="str">
         <f ca="1">TEXT(NOW(), "mmdd")</f>
         <v>0315</v>
       </c>
-      <c r="I8" s="49" t="str">
+      <c r="I8" s="33" t="str">
         <f ca="1">TEXT(NOW(), "hhmm")</f>
-        <v>1704</v>
-      </c>
-      <c r="J8" s="50" t="str">
+        <v>2327</v>
+      </c>
+      <c r="J8" s="34" t="str">
         <f ca="1">"["&amp;D8&amp;"]-["&amp;E8&amp;"]-["&amp;F8&amp;"]-["&amp;G8&amp;"]-["&amp;TEXT(H8,"0000")&amp;"]-["&amp;TEXT(I8,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704]</v>
-      </c>
-      <c r="K8" s="51"/>
-      <c r="L8" s="52"/>
-    </row>
-    <row r="9" spans="2:12" s="22" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="53"/>
-      <c r="C9" s="53"/>
-      <c r="D9" s="54"/>
-      <c r="E9" s="54"/>
-      <c r="F9" s="54"/>
-      <c r="G9" s="54"/>
-      <c r="H9" s="55"/>
-      <c r="I9" s="56"/>
-      <c r="J9" s="54"/>
-      <c r="K9" s="54"/>
-      <c r="L9" s="54"/>
+        <v>[1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327]</v>
+      </c>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+    </row>
+    <row r="9" spans="2:12" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="35"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="38"/>
+      <c r="J9" s="36"/>
+      <c r="K9" s="36"/>
+      <c r="L9" s="36"/>
     </row>
     <row r="10" spans="2:12" ht="33" x14ac:dyDescent="0.3">
-      <c r="B10" s="44" t="s">
+      <c r="B10" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C10" s="45" t="s">
+      <c r="C10" s="39" t="s">
         <v>64</v>
       </c>
-      <c r="D10" s="44" t="s">
+      <c r="D10" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="E10" s="44" t="s">
+      <c r="E10" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="44" t="s">
+      <c r="G10" s="29" t="s">
         <v>32</v>
       </c>
-      <c r="H10" s="44" t="s">
+      <c r="H10" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="I10" s="44" t="s">
+      <c r="I10" s="29" t="s">
         <v>29</v>
       </c>
-      <c r="J10" s="44" t="s">
+      <c r="J10" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="K10" s="44" t="s">
+      <c r="K10" s="29" t="s">
         <v>33</v>
       </c>
-      <c r="L10" s="44" t="s">
+      <c r="L10" s="29" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="9" t="s">
+      <c r="B11" s="40" t="s">
         <v>0</v>
       </c>
-      <c r="C11" s="10"/>
-      <c r="D11" s="10">
+      <c r="C11" s="41"/>
+      <c r="D11" s="41">
         <v>10</v>
       </c>
-      <c r="E11" s="10"/>
-      <c r="F11" s="10"/>
-      <c r="G11" s="10"/>
-      <c r="H11" s="8"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="8"/>
-      <c r="K11" s="8"/>
-      <c r="L11" s="11" t="str">
+      <c r="E11" s="41"/>
+      <c r="F11" s="41"/>
+      <c r="G11" s="41"/>
+      <c r="H11" s="29"/>
+      <c r="I11" s="29"/>
+      <c r="J11" s="29"/>
+      <c r="K11" s="29"/>
+      <c r="L11" s="42" t="str">
         <f ca="1">C11&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / 지금:"&amp;E11&amp;" / 근거:"&amp;F11&amp;" / 요청:"&amp;G11&amp;" / "&amp;D11)</f>
-        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704] / 지금: / 근거: / 요청: / 10</v>
+        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327] / 지금: / 근거: / 요청: / 10</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="C12" s="8"/>
-      <c r="D12" s="8"/>
-      <c r="E12" s="8"/>
-      <c r="F12" s="8"/>
-      <c r="G12" s="8"/>
-      <c r="H12" s="60"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="8"/>
-      <c r="K12" s="8"/>
-      <c r="L12" s="11" t="str">
+      <c r="C12" s="29"/>
+      <c r="D12" s="29"/>
+      <c r="E12" s="29"/>
+      <c r="F12" s="29"/>
+      <c r="G12" s="29"/>
+      <c r="H12" s="43"/>
+      <c r="I12" s="41"/>
+      <c r="J12" s="29"/>
+      <c r="K12" s="29"/>
+      <c r="L12" s="42" t="str">
         <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H12="","{사유코드}",H12)&amp;" / 다음확인 "&amp;I12&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="9" t="s">
+      <c r="B13" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="8"/>
-      <c r="D13" s="8"/>
-      <c r="E13" s="8"/>
-      <c r="F13" s="8"/>
-      <c r="G13" s="8"/>
-      <c r="H13" s="60"/>
-      <c r="I13" s="10"/>
-      <c r="J13" s="8"/>
-      <c r="K13" s="8"/>
-      <c r="L13" s="11" t="str">
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="29"/>
+      <c r="F13" s="29"/>
+      <c r="G13" s="29"/>
+      <c r="H13" s="43"/>
+      <c r="I13" s="41"/>
+      <c r="J13" s="29"/>
+      <c r="K13" s="29"/>
+      <c r="L13" s="42" t="str">
         <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H13="","{사유코드}",H13)&amp;" / 다음확인 "&amp;I13&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="9" t="s">
+      <c r="B14" s="40" t="s">
         <v>1</v>
       </c>
-      <c r="C14" s="8"/>
-      <c r="D14" s="8"/>
-      <c r="E14" s="10"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
-      <c r="I14" s="8"/>
-      <c r="J14" s="10" t="s">
+      <c r="C14" s="29"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="41"/>
+      <c r="F14" s="29"/>
+      <c r="G14" s="29"/>
+      <c r="H14" s="29"/>
+      <c r="I14" s="29"/>
+      <c r="J14" s="41" t="s">
         <v>70</v>
       </c>
-      <c r="K14" s="10"/>
-      <c r="L14" s="11" t="str">
+      <c r="K14" s="41"/>
+      <c r="L14" s="42" t="str">
         <f ca="1">IF($J$8="","", "[D]"&amp;$J$8&amp;" / 결과:"&amp;E14&amp;" / 현재:"&amp;J14&amp;" / F/U:"&amp;K14)</f>
-        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704] / 결과: / 현재:처방확인 / F/U:</v>
+        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327] / 결과: / 현재:처방확인 / F/U:</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="9" t="s">
+      <c r="B15" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="60"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="8"/>
-      <c r="H15" s="8"/>
-      <c r="I15" s="8"/>
-      <c r="J15" s="8"/>
-      <c r="K15" s="8"/>
-      <c r="L15" s="11" t="str">
+      <c r="C15" s="29"/>
+      <c r="D15" s="29"/>
+      <c r="E15" s="43"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="29"/>
+      <c r="H15" s="29"/>
+      <c r="I15" s="29"/>
+      <c r="J15" s="29"/>
+      <c r="K15" s="29"/>
+      <c r="L15" s="42" t="str">
         <f ca="1">IF($J$8="","", "(보고)"&amp;$J$8&amp;"/"&amp;E15&amp;IF(E15="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704]/12</v>
+        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327]/12</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="8" t="s">
+      <c r="B16" s="29" t="s">
         <v>2</v>
       </c>
-      <c r="C16" s="26" t="s">
+      <c r="C16" s="44" t="s">
         <v>73</v>
       </c>
-      <c r="D16" s="26"/>
-      <c r="E16" s="27" t="s">
+      <c r="D16" s="44"/>
+      <c r="E16" s="30" t="s">
         <v>74</v>
       </c>
-      <c r="F16" s="27"/>
-      <c r="G16" s="27"/>
-      <c r="H16" s="27"/>
-      <c r="I16" s="27" t="s">
+      <c r="F16" s="30"/>
+      <c r="G16" s="30"/>
+      <c r="H16" s="30"/>
+      <c r="I16" s="30" t="s">
         <v>75</v>
       </c>
-      <c r="J16" s="27"/>
-      <c r="K16" s="27"/>
-      <c r="L16" s="8"/>
+      <c r="J16" s="30"/>
+      <c r="K16" s="30"/>
+      <c r="L16" s="29"/>
     </row>
     <row r="17" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="40" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
-      <c r="K17" s="28"/>
-      <c r="L17" s="11" t="str">
+      <c r="C17" s="45"/>
+      <c r="D17" s="45"/>
+      <c r="E17" s="45"/>
+      <c r="F17" s="45"/>
+      <c r="G17" s="45"/>
+      <c r="H17" s="45"/>
+      <c r="I17" s="45"/>
+      <c r="J17" s="45"/>
+      <c r="K17" s="45"/>
+      <c r="L17" s="42" t="str">
         <f ca="1">IF($J$8="","", "[A][야간이음기록]"&amp;$J$8&amp;"/지금:"&amp;C17&amp;"/조치:"&amp;E17&amp;"/[D]"&amp;E17&amp;I17)</f>
-        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0315]-[1704]/지금:/조치:/[D]</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="12"/>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
-      <c r="J18" s="13"/>
-      <c r="K18" s="13"/>
-      <c r="L18" s="14"/>
-    </row>
+        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327]/지금:/조치:/[D]</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" s="8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:12" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="46" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="25"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="25"/>
-      <c r="F19" s="25"/>
-      <c r="G19" s="25"/>
-      <c r="H19" s="25"/>
-      <c r="I19" s="25"/>
-      <c r="J19" s="25"/>
-      <c r="K19" s="25"/>
-      <c r="L19" s="25"/>
+      <c r="C19" s="46"/>
+      <c r="D19" s="46"/>
+      <c r="E19" s="46"/>
+      <c r="F19" s="46"/>
+      <c r="G19" s="46"/>
+      <c r="H19" s="46"/>
+      <c r="I19" s="46"/>
+      <c r="J19" s="46"/>
+      <c r="K19" s="46"/>
+      <c r="L19" s="46"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1883,7 +1744,7 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="10">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="10">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$A$2:$A$4</xm:f>
@@ -2002,11 +1863,11 @@
       <c r="D2" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="F2" s="15" t="s">
         <v>56</v>
       </c>
-      <c r="G2" s="33"/>
-      <c r="H2" s="33"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="16"/>
       <c r="J2" s="5" t="s">
         <v>35</v>
       </c>
@@ -2025,9 +1886,9 @@
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="33"/>
-      <c r="G3" s="33"/>
-      <c r="H3" s="33"/>
+      <c r="F3" s="16"/>
+      <c r="G3" s="16"/>
+      <c r="H3" s="16"/>
       <c r="J3" s="5" t="s">
         <v>36</v>
       </c>
@@ -2046,9 +1907,9 @@
       <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="33"/>
-      <c r="G4" s="33"/>
-      <c r="H4" s="33"/>
+      <c r="F4" s="16"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="16"/>
       <c r="J4" s="5" t="s">
         <v>37</v>
       </c>
@@ -2158,81 +2019,81 @@
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="19" t="s">
+      <c r="A23" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="B23" s="18" t="s">
+      <c r="B23" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="D23" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E23" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="G23" s="11" t="s">
+        <v>103</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="J23" s="11" t="s">
+        <v>104</v>
+      </c>
+      <c r="K23" s="11">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B24" s="9" t="s">
         <v>85</v>
       </c>
-      <c r="D23" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="E23" s="7" t="s">
+      <c r="E24" s="7" t="s">
         <v>92</v>
       </c>
-      <c r="G23" s="21" t="s">
-        <v>104</v>
-      </c>
-      <c r="H23" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="J23" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="K23" s="21">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B24" s="18" t="s">
+      <c r="H24" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="K24" s="11">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B25" s="9" t="s">
         <v>86</v>
       </c>
-      <c r="E24" s="7" t="s">
+      <c r="E25" s="7" t="s">
         <v>93</v>
       </c>
-      <c r="H24" s="21" t="s">
-        <v>102</v>
-      </c>
-      <c r="K24" s="21">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B25" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H25" s="57" t="s">
-        <v>101</v>
-      </c>
-      <c r="K25" s="21">
+      <c r="H25" s="14" t="s">
+        <v>100</v>
+      </c>
+      <c r="K25" s="11">
         <v>141</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E26" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="H26" s="21" t="s">
-        <v>100</v>
-      </c>
-      <c r="K26" s="21">
+        <v>94</v>
+      </c>
+      <c r="H26" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="K26" s="11">
         <v>142</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E27" s="7" t="s">
-        <v>96</v>
-      </c>
-      <c r="H27" s="21" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="11" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H28" s="11" t="s">
         <v>98</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H28" s="21" t="s">
-        <v>99</v>
       </c>
     </row>
   </sheetData>

--- a/documents/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents/WeValue_현장ACD_메신저템플릿.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahee\Desktop\GitHub동기화폴더\2026-QI\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EFFAFA4-7CD9-4F9C-BC7E-7108EF172574}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1370D50-8485-48F0-B673-081161F037A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -332,10 +332,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>WeValue 현장ACD 메신저 템플릿</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>14층 코드</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -575,6 +571,10 @@
   </si>
   <si>
     <t>CASE ID</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>WeValue 현장ACD 메신저 템플릿 ( v1.260316 )</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -869,110 +869,110 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1334,380 +1334,380 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" s="8" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="48" t="s">
-        <v>41</v>
-      </c>
-      <c r="C1" s="48"/>
-      <c r="D1" s="49"/>
-      <c r="E1" s="49"/>
-      <c r="F1" s="49"/>
-      <c r="G1" s="49"/>
-      <c r="H1" s="49"/>
-      <c r="I1" s="49"/>
-      <c r="J1" s="49"/>
-      <c r="K1" s="49"/>
-      <c r="L1" s="49"/>
+      <c r="B1" s="36" t="s">
+        <v>107</v>
+      </c>
+      <c r="C1" s="36"/>
+      <c r="D1" s="37"/>
+      <c r="E1" s="37"/>
+      <c r="F1" s="37"/>
+      <c r="G1" s="37"/>
+      <c r="H1" s="37"/>
+      <c r="I1" s="37"/>
+      <c r="J1" s="37"/>
+      <c r="K1" s="37"/>
+      <c r="L1" s="37"/>
     </row>
     <row r="2" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="47" t="s">
-        <v>83</v>
-      </c>
-      <c r="C2" s="47"/>
-      <c r="D2" s="47"/>
-      <c r="E2" s="47"/>
-      <c r="F2" s="47"/>
-      <c r="G2" s="47"/>
-      <c r="H2" s="47"/>
-      <c r="I2" s="47"/>
-      <c r="J2" s="47"/>
-      <c r="K2" s="47"/>
-      <c r="L2" s="47"/>
+      <c r="B2" s="44" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="44"/>
+      <c r="D2" s="44"/>
+      <c r="E2" s="44"/>
+      <c r="F2" s="44"/>
+      <c r="G2" s="44"/>
+      <c r="H2" s="44"/>
+      <c r="I2" s="44"/>
+      <c r="J2" s="44"/>
+      <c r="K2" s="44"/>
+      <c r="L2" s="44"/>
     </row>
     <row r="3" spans="2:12" s="13" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="C3" s="18" t="s">
+      <c r="B3" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="D3" s="16">
+        <v>92</v>
+      </c>
+      <c r="E3" s="15" t="s">
         <v>76</v>
       </c>
-      <c r="D3" s="19">
-        <v>92</v>
-      </c>
-      <c r="E3" s="18" t="s">
+      <c r="F3" s="16" t="s">
+        <v>104</v>
+      </c>
+      <c r="G3" s="15" t="s">
         <v>77</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="H3" s="16" t="s">
         <v>105</v>
       </c>
-      <c r="G3" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="I3" s="20" t="s">
+      <c r="I3" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="J3" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="K3" s="20"/>
-      <c r="L3" s="22" t="str">
+      <c r="K3" s="17"/>
+      <c r="L3" s="19" t="str">
         <f>"["&amp;D3&amp;"/"&amp;F3&amp;"/"&amp;H3&amp;"] "&amp;J3</f>
         <v>[92/나이트/B] 이OO</v>
       </c>
     </row>
     <row r="4" spans="2:12" s="13" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="18" t="s">
+      <c r="B4" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="18" t="s">
+      <c r="D4" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="E4" s="42" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E4" s="23" t="s">
-        <v>82</v>
-      </c>
-      <c r="F4" s="23"/>
-      <c r="G4" s="24" t="s">
+      <c r="F4" s="42"/>
+      <c r="G4" s="43" t="s">
+        <v>86</v>
+      </c>
+      <c r="H4" s="43"/>
+      <c r="I4" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="H4" s="24"/>
-      <c r="I4" s="20" t="s">
+      <c r="J4" s="18" t="s">
         <v>88</v>
       </c>
-      <c r="J4" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="K4" s="20"/>
-      <c r="L4" s="22" t="str">
+      <c r="K4" s="17"/>
+      <c r="L4" s="19" t="str">
         <f>"["&amp;D4&amp;"/"&amp;G4&amp;"] "&amp;J4</f>
         <v>[141-MH/KJS] 이OO</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26"/>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26"/>
-      <c r="K5" s="26"/>
-      <c r="L5" s="27"/>
+      <c r="B5" s="20"/>
+      <c r="C5" s="20"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="22"/>
     </row>
     <row r="6" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="17" t="s">
-        <v>107</v>
-      </c>
-      <c r="C6" s="17"/>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="17"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="17"/>
+      <c r="B6" s="46" t="s">
+        <v>106</v>
+      </c>
+      <c r="C6" s="46"/>
+      <c r="D6" s="46"/>
+      <c r="E6" s="46"/>
+      <c r="F6" s="46"/>
+      <c r="G6" s="46"/>
+      <c r="H6" s="46"/>
+      <c r="I6" s="46"/>
+      <c r="J6" s="46"/>
+      <c r="K6" s="46"/>
+      <c r="L6" s="46"/>
     </row>
     <row r="7" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29" t="s">
+      <c r="B7" s="45"/>
+      <c r="C7" s="45"/>
+      <c r="D7" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="29" t="s">
+      <c r="E7" s="23" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="29" t="s">
+      <c r="F7" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="23" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="29" t="s">
+      <c r="H7" s="23" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="29" t="s">
+      <c r="I7" s="23" t="s">
         <v>28</v>
       </c>
-      <c r="J7" s="30" t="s">
+      <c r="J7" s="40" t="s">
         <v>27</v>
       </c>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
+      <c r="K7" s="40"/>
+      <c r="L7" s="40"/>
     </row>
     <row r="8" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="31">
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="24">
         <v>1311</v>
       </c>
-      <c r="E8" s="31">
+      <c r="E8" s="24">
         <v>12345678</v>
       </c>
-      <c r="F8" s="31" t="s">
+      <c r="F8" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="G8" s="31" t="s">
+      <c r="G8" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="25" t="str">
+        <f ca="1">TEXT(NOW(), "mmdd")</f>
+        <v>0316</v>
+      </c>
+      <c r="I8" s="26" t="str">
+        <f ca="1">TEXT(NOW(), "hhmm")</f>
+        <v>0033</v>
+      </c>
+      <c r="J8" s="47" t="str">
+        <f ca="1">"["&amp;D8&amp;"]-["&amp;E8&amp;"]-["&amp;F8&amp;"]-["&amp;G8&amp;"]-["&amp;TEXT(H8,"0000")&amp;"]-["&amp;TEXT(I8,"0000")&amp;"]"</f>
+        <v>[1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033]</v>
+      </c>
+      <c r="K8" s="47"/>
+      <c r="L8" s="47"/>
+    </row>
+    <row r="9" spans="2:12" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="27"/>
+      <c r="C9" s="27"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="28"/>
+      <c r="F9" s="28"/>
+      <c r="G9" s="28"/>
+      <c r="H9" s="29"/>
+      <c r="I9" s="30"/>
+      <c r="J9" s="28"/>
+      <c r="K9" s="28"/>
+      <c r="L9" s="28"/>
+    </row>
+    <row r="10" spans="2:12" ht="33" x14ac:dyDescent="0.3">
+      <c r="B10" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C10" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="E10" s="23" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="23" t="s">
+        <v>31</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>32</v>
+      </c>
+      <c r="H10" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="I10" s="23" t="s">
+        <v>29</v>
+      </c>
+      <c r="J10" s="23" t="s">
+        <v>5</v>
+      </c>
+      <c r="K10" s="23" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="23" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="32" t="s">
+        <v>0</v>
+      </c>
+      <c r="C11" s="33"/>
+      <c r="D11" s="33">
+        <v>10</v>
+      </c>
+      <c r="E11" s="33"/>
+      <c r="F11" s="33"/>
+      <c r="G11" s="33"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="23"/>
+      <c r="J11" s="23"/>
+      <c r="K11" s="23"/>
+      <c r="L11" s="34" t="str">
+        <f ca="1">C11&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / 지금:"&amp;E11&amp;" / 근거:"&amp;F11&amp;" / 요청:"&amp;G11&amp;" / "&amp;D11)</f>
+        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033] / 지금: / 근거: / 요청: / 10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="32" t="s">
+        <v>65</v>
+      </c>
+      <c r="C12" s="23"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="23"/>
+      <c r="F12" s="23"/>
+      <c r="G12" s="23"/>
+      <c r="H12" s="35"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="23"/>
+      <c r="K12" s="23"/>
+      <c r="L12" s="34" t="str">
+        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H12="","{사유코드}",H12)&amp;" / 다음확인 "&amp;I12&amp;" (전화 1회 후)")</f>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="32" t="s">
+        <v>66</v>
+      </c>
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="23"/>
+      <c r="F13" s="23"/>
+      <c r="G13" s="23"/>
+      <c r="H13" s="35"/>
+      <c r="I13" s="33"/>
+      <c r="J13" s="23"/>
+      <c r="K13" s="23"/>
+      <c r="L13" s="34" t="str">
+        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H13="","{사유코드}",H13)&amp;" / 다음확인 "&amp;I13&amp;" (전화 1회 후)")</f>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="33"/>
+      <c r="F14" s="23"/>
+      <c r="G14" s="23"/>
+      <c r="H14" s="23"/>
+      <c r="I14" s="23"/>
+      <c r="J14" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="K14" s="33"/>
+      <c r="L14" s="34" t="str">
+        <f ca="1">IF($J$8="","", "[D]"&amp;$J$8&amp;" / 결과:"&amp;E14&amp;" / 현재:"&amp;J14&amp;" / F/U:"&amp;K14)</f>
+        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033] / 결과: / 현재:처방확인 / F/U:</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="32" t="s">
+        <v>34</v>
+      </c>
+      <c r="C15" s="23"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="35"/>
+      <c r="F15" s="23"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
+      <c r="I15" s="23"/>
+      <c r="J15" s="23"/>
+      <c r="K15" s="23"/>
+      <c r="L15" s="34" t="str">
+        <f ca="1">IF($J$8="","", "(보고)"&amp;$J$8&amp;"/"&amp;E15&amp;IF(E15="","","/")&amp;"12")</f>
+        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033]/12</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="23" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="39" t="s">
+        <v>72</v>
+      </c>
+      <c r="D16" s="39"/>
+      <c r="E16" s="40" t="s">
+        <v>73</v>
+      </c>
+      <c r="F16" s="40"/>
+      <c r="G16" s="40"/>
+      <c r="H16" s="40"/>
+      <c r="I16" s="40" t="s">
+        <v>74</v>
+      </c>
+      <c r="J16" s="40"/>
+      <c r="K16" s="40"/>
+      <c r="L16" s="23"/>
+    </row>
+    <row r="17" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="32" t="s">
         <v>71</v>
       </c>
-      <c r="H8" s="32" t="str">
-        <f ca="1">TEXT(NOW(), "mmdd")</f>
-        <v>0315</v>
-      </c>
-      <c r="I8" s="33" t="str">
-        <f ca="1">TEXT(NOW(), "hhmm")</f>
-        <v>2327</v>
-      </c>
-      <c r="J8" s="34" t="str">
-        <f ca="1">"["&amp;D8&amp;"]-["&amp;E8&amp;"]-["&amp;F8&amp;"]-["&amp;G8&amp;"]-["&amp;TEXT(H8,"0000")&amp;"]-["&amp;TEXT(I8,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327]</v>
-      </c>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-    </row>
-    <row r="9" spans="2:12" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="35"/>
-      <c r="C9" s="35"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="38"/>
-      <c r="J9" s="36"/>
-      <c r="K9" s="36"/>
-      <c r="L9" s="36"/>
-    </row>
-    <row r="10" spans="2:12" ht="33" x14ac:dyDescent="0.3">
-      <c r="B10" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="39" t="s">
-        <v>64</v>
-      </c>
-      <c r="D10" s="29" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="29" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="29" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="29" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="29" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="29" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" s="29" t="s">
-        <v>33</v>
-      </c>
-      <c r="L10" s="29" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="40" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41">
-        <v>10</v>
-      </c>
-      <c r="E11" s="41"/>
-      <c r="F11" s="41"/>
-      <c r="G11" s="41"/>
-      <c r="H11" s="29"/>
-      <c r="I11" s="29"/>
-      <c r="J11" s="29"/>
-      <c r="K11" s="29"/>
-      <c r="L11" s="42" t="str">
-        <f ca="1">C11&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / 지금:"&amp;E11&amp;" / 근거:"&amp;F11&amp;" / 요청:"&amp;G11&amp;" / "&amp;D11)</f>
-        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327] / 지금: / 근거: / 요청: / 10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="C12" s="29"/>
-      <c r="D12" s="29"/>
-      <c r="E12" s="29"/>
-      <c r="F12" s="29"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="43"/>
-      <c r="I12" s="41"/>
-      <c r="J12" s="29"/>
-      <c r="K12" s="29"/>
-      <c r="L12" s="42" t="str">
-        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H12="","{사유코드}",H12)&amp;" / 다음확인 "&amp;I12&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="29"/>
-      <c r="F13" s="29"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="43"/>
-      <c r="I13" s="41"/>
-      <c r="J13" s="29"/>
-      <c r="K13" s="29"/>
-      <c r="L13" s="42" t="str">
-        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H13="","{사유코드}",H13)&amp;" / 다음확인 "&amp;I13&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="40" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="29"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="41"/>
-      <c r="F14" s="29"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="29"/>
-      <c r="J14" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="K14" s="41"/>
-      <c r="L14" s="42" t="str">
-        <f ca="1">IF($J$8="","", "[D]"&amp;$J$8&amp;" / 결과:"&amp;E14&amp;" / 현재:"&amp;J14&amp;" / F/U:"&amp;K14)</f>
-        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327] / 결과: / 현재:처방확인 / F/U:</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="40" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="29"/>
-      <c r="D15" s="29"/>
-      <c r="E15" s="43"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="29"/>
-      <c r="J15" s="29"/>
-      <c r="K15" s="29"/>
-      <c r="L15" s="42" t="str">
-        <f ca="1">IF($J$8="","", "(보고)"&amp;$J$8&amp;"/"&amp;E15&amp;IF(E15="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327]/12</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="29" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="44" t="s">
-        <v>73</v>
-      </c>
-      <c r="D16" s="44"/>
-      <c r="E16" s="30" t="s">
-        <v>74</v>
-      </c>
-      <c r="F16" s="30"/>
-      <c r="G16" s="30"/>
-      <c r="H16" s="30"/>
-      <c r="I16" s="30" t="s">
-        <v>75</v>
-      </c>
-      <c r="J16" s="30"/>
-      <c r="K16" s="30"/>
-      <c r="L16" s="29"/>
-    </row>
-    <row r="17" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="40" t="s">
-        <v>72</v>
-      </c>
-      <c r="C17" s="45"/>
-      <c r="D17" s="45"/>
-      <c r="E17" s="45"/>
-      <c r="F17" s="45"/>
-      <c r="G17" s="45"/>
-      <c r="H17" s="45"/>
-      <c r="I17" s="45"/>
-      <c r="J17" s="45"/>
-      <c r="K17" s="45"/>
-      <c r="L17" s="42" t="str">
+      <c r="C17" s="41"/>
+      <c r="D17" s="41"/>
+      <c r="E17" s="41"/>
+      <c r="F17" s="41"/>
+      <c r="G17" s="41"/>
+      <c r="H17" s="41"/>
+      <c r="I17" s="41"/>
+      <c r="J17" s="41"/>
+      <c r="K17" s="41"/>
+      <c r="L17" s="34" t="str">
         <f ca="1">IF($J$8="","", "[A][야간이음기록]"&amp;$J$8&amp;"/지금:"&amp;C17&amp;"/조치:"&amp;E17&amp;"/[D]"&amp;E17&amp;I17)</f>
-        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0315]-[2327]/지금:/조치:/[D]</v>
+        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033]/지금:/조치:/[D]</v>
       </c>
     </row>
     <row r="18" spans="2:12" s="8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="19" spans="2:12" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="46" t="s">
+      <c r="B19" s="38" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="46"/>
-      <c r="D19" s="46"/>
-      <c r="E19" s="46"/>
-      <c r="F19" s="46"/>
-      <c r="G19" s="46"/>
-      <c r="H19" s="46"/>
-      <c r="I19" s="46"/>
-      <c r="J19" s="46"/>
-      <c r="K19" s="46"/>
-      <c r="L19" s="46"/>
+      <c r="C19" s="38"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="38"/>
+      <c r="H19" s="38"/>
+      <c r="I19" s="38"/>
+      <c r="J19" s="38"/>
+      <c r="K19" s="38"/>
+      <c r="L19" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="15">
@@ -1835,10 +1835,10 @@
         <v>6</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>68</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>69</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>7</v>
@@ -1849,7 +1849,7 @@
         <v>38</v>
       </c>
       <c r="L1" s="4" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M1" s="4"/>
     </row>
@@ -1861,22 +1861,22 @@
         <v>8</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="F2" s="15" t="s">
-        <v>56</v>
-      </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
+        <v>64</v>
+      </c>
+      <c r="F2" s="48" t="s">
+        <v>55</v>
+      </c>
+      <c r="G2" s="49"/>
+      <c r="H2" s="49"/>
       <c r="J2" s="5" t="s">
         <v>35</v>
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="M2" s="4" t="s">
         <v>43</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -1886,18 +1886,18 @@
       <c r="B3" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
+      <c r="F3" s="49"/>
+      <c r="G3" s="49"/>
+      <c r="H3" s="49"/>
       <c r="J3" s="5" t="s">
         <v>36</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="M3" s="4" t="s">
         <v>45</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -1907,18 +1907,18 @@
       <c r="B4" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
+      <c r="H4" s="49"/>
       <c r="J4" s="5" t="s">
         <v>37</v>
       </c>
       <c r="K4" s="6"/>
       <c r="L4" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
@@ -1926,10 +1926,10 @@
         <v>11</v>
       </c>
       <c r="L5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M5" s="4" t="s">
         <v>48</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
@@ -1937,10 +1937,10 @@
         <v>12</v>
       </c>
       <c r="L6" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="M6" s="4" t="s">
         <v>50</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
@@ -1948,10 +1948,10 @@
         <v>13</v>
       </c>
       <c r="L7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="M7" s="4" t="s">
         <v>52</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
@@ -1959,10 +1959,10 @@
         <v>14</v>
       </c>
       <c r="L8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="M8" s="4" t="s">
         <v>54</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
@@ -1970,10 +1970,10 @@
         <v>15</v>
       </c>
       <c r="L9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="M9" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
@@ -1981,10 +1981,10 @@
         <v>16</v>
       </c>
       <c r="L10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="M10" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>61</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
@@ -1992,10 +1992,10 @@
         <v>17</v>
       </c>
       <c r="L11" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>63</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
@@ -2015,30 +2015,30 @@
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A23" s="10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D23" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E23" s="7" t="s">
         <v>90</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>91</v>
-      </c>
       <c r="G23" s="11" t="s">
+        <v>102</v>
+      </c>
+      <c r="H23" s="11" t="s">
+        <v>101</v>
+      </c>
+      <c r="J23" s="11" t="s">
         <v>103</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>104</v>
       </c>
       <c r="K23" s="11">
         <v>92</v>
@@ -2046,13 +2046,13 @@
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B24" s="9" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E24" s="7" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H24" s="11" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="K24" s="11">
         <v>131</v>
@@ -2060,13 +2060,13 @@
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B25" s="9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E25" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="H25" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="K25" s="11">
         <v>141</v>
@@ -2074,10 +2074,10 @@
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E26" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="H26" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K26" s="11">
         <v>142</v>
@@ -2085,15 +2085,15 @@
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.3">
       <c r="E27" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H27" s="11" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.3">
       <c r="H28" s="11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/documents/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents/WeValue_현장ACD_메신저템플릿.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr codeName="현재_통합_문서"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rahee\Desktop\GitHub동기화폴더\2026-QI\documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lds85\Desktop\임덕수\git\2026-QI\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1370D50-8485-48F0-B673-081161F037A2}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77E4C1A-F2DF-4844-A85A-C49AFAE360AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="25815" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="소통메신저 양식 자동완성" sheetId="2" r:id="rId1"/>
@@ -182,10 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="108">
-  <si>
-    <t>A(보고)</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="123">
   <si>
     <t>D(완료)</t>
   </si>
@@ -285,16 +282,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>지금
-(핵심)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>근거
-(데이터)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>요청
 (평가/조치)</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -332,10 +319,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>14층 코드</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>[CHEMO]</t>
   </si>
   <si>
@@ -400,11 +383,6 @@
     <t>퇴원·전과·사망 관리 (Discharge/Death)</t>
   </si>
   <si>
-    <t>141W,142W 전용
-"하이패스" 태그</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>IN-OUT(인계)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -575,6 +553,89 @@
   </si>
   <si>
     <t>WeValue 현장ACD 메신저 템플릿 ( v1.260316 )</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금
+(핵심)
+근거
+(데이터)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[응급]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[상태변화]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[퇴원]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[수술전/후]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[검사전/후]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[동의서]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[협진]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[수혈]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[회진후]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[기타]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[입원]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[자가약]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>[EMR확인]</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>PA만 입력 가능</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>병동공통태그</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>14층 태그</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>태그</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A(공통)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>A(14층전용)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -746,7 +807,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="8">
     <border>
       <left/>
       <right/>
@@ -821,11 +882,37 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -845,134 +932,146 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="178" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1314,11 +1413,11 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:L19"/>
+  <dimension ref="B1:L20"/>
   <sheetFormatPr defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.75" style="1" customWidth="1"/>
-    <col min="2" max="2" width="19.375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="26.875" style="1" customWidth="1"/>
     <col min="3" max="3" width="21.875" style="1" customWidth="1"/>
     <col min="4" max="4" width="16.625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.5" style="1" bestFit="1" customWidth="1"/>
@@ -1333,392 +1432,415 @@
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" s="8" customFormat="1" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="36" t="s">
-        <v>107</v>
-      </c>
-      <c r="C1" s="36"/>
-      <c r="D1" s="37"/>
-      <c r="E1" s="37"/>
-      <c r="F1" s="37"/>
-      <c r="G1" s="37"/>
-      <c r="H1" s="37"/>
-      <c r="I1" s="37"/>
-      <c r="J1" s="37"/>
-      <c r="K1" s="37"/>
-      <c r="L1" s="37"/>
+    <row r="1" spans="2:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B1" s="33" t="s">
+        <v>102</v>
+      </c>
+      <c r="C1" s="33"/>
+      <c r="D1" s="34"/>
+      <c r="E1" s="34"/>
+      <c r="F1" s="34"/>
+      <c r="G1" s="34"/>
+      <c r="H1" s="34"/>
+      <c r="I1" s="34"/>
+      <c r="J1" s="34"/>
+      <c r="K1" s="34"/>
+      <c r="L1" s="34"/>
     </row>
     <row r="2" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="44" t="s">
+      <c r="B2" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="C2" s="41"/>
+      <c r="D2" s="41"/>
+      <c r="E2" s="41"/>
+      <c r="F2" s="41"/>
+      <c r="G2" s="41"/>
+      <c r="H2" s="41"/>
+      <c r="I2" s="41"/>
+      <c r="J2" s="41"/>
+      <c r="K2" s="41"/>
+      <c r="L2" s="41"/>
+    </row>
+    <row r="3" spans="2:12" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B3" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="D3" s="13">
+        <v>92</v>
+      </c>
+      <c r="E3" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="G3" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>82</v>
       </c>
-      <c r="C2" s="44"/>
-      <c r="D2" s="44"/>
-      <c r="E2" s="44"/>
-      <c r="F2" s="44"/>
-      <c r="G2" s="44"/>
-      <c r="H2" s="44"/>
-      <c r="I2" s="44"/>
-      <c r="J2" s="44"/>
-      <c r="K2" s="44"/>
-      <c r="L2" s="44"/>
-    </row>
-    <row r="3" spans="2:12" s="13" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B3" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="D3" s="16">
-        <v>92</v>
-      </c>
-      <c r="E3" s="15" t="s">
-        <v>76</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>104</v>
-      </c>
-      <c r="G3" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="I3" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="J3" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="K3" s="17"/>
-      <c r="L3" s="19" t="str">
+      <c r="J3" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="K3" s="14"/>
+      <c r="L3" s="16" t="str">
         <f>"["&amp;D3&amp;"/"&amp;F3&amp;"/"&amp;H3&amp;"] "&amp;J3</f>
         <v>[92/나이트/B] 이OO</v>
       </c>
     </row>
-    <row r="4" spans="2:12" s="13" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B4" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="D4" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E4" s="42" t="s">
+    <row r="4" spans="2:12" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="C4" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="D4" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>76</v>
+      </c>
+      <c r="F4" s="39"/>
+      <c r="G4" s="40" t="s">
         <v>81</v>
       </c>
-      <c r="F4" s="42"/>
-      <c r="G4" s="43" t="s">
-        <v>86</v>
-      </c>
-      <c r="H4" s="43"/>
-      <c r="I4" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="J4" s="18" t="s">
-        <v>88</v>
-      </c>
-      <c r="K4" s="17"/>
-      <c r="L4" s="19" t="str">
+      <c r="H4" s="40"/>
+      <c r="I4" s="14" t="s">
+        <v>82</v>
+      </c>
+      <c r="J4" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="K4" s="14"/>
+      <c r="L4" s="16" t="str">
         <f>"["&amp;D4&amp;"/"&amp;G4&amp;"] "&amp;J4</f>
         <v>[141-MH/KJS] 이OO</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="20"/>
-      <c r="C5" s="20"/>
-      <c r="D5" s="21"/>
-      <c r="E5" s="21"/>
-      <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="J5" s="21"/>
-      <c r="K5" s="21"/>
-      <c r="L5" s="22"/>
+      <c r="B5" s="17"/>
+      <c r="C5" s="17"/>
+      <c r="D5" s="18"/>
+      <c r="E5" s="18"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="J5" s="18"/>
+      <c r="K5" s="18"/>
+      <c r="L5" s="19"/>
     </row>
     <row r="6" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="46" t="s">
-        <v>106</v>
-      </c>
-      <c r="C6" s="46"/>
-      <c r="D6" s="46"/>
-      <c r="E6" s="46"/>
-      <c r="F6" s="46"/>
-      <c r="G6" s="46"/>
-      <c r="H6" s="46"/>
-      <c r="I6" s="46"/>
-      <c r="J6" s="46"/>
-      <c r="K6" s="46"/>
-      <c r="L6" s="46"/>
+      <c r="B6" s="43" t="s">
+        <v>101</v>
+      </c>
+      <c r="C6" s="43"/>
+      <c r="D6" s="43"/>
+      <c r="E6" s="43"/>
+      <c r="F6" s="43"/>
+      <c r="G6" s="43"/>
+      <c r="H6" s="43"/>
+      <c r="I6" s="43"/>
+      <c r="J6" s="43"/>
+      <c r="K6" s="43"/>
+      <c r="L6" s="43"/>
     </row>
     <row r="7" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="45"/>
-      <c r="C7" s="45"/>
-      <c r="D7" s="23" t="s">
+      <c r="B7" s="42"/>
+      <c r="C7" s="42"/>
+      <c r="D7" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="20" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="F7" s="20" t="s">
         <v>22</v>
       </c>
-      <c r="F7" s="23" t="s">
+      <c r="G7" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="23" t="s">
+      <c r="H7" s="20" t="s">
         <v>24</v>
       </c>
-      <c r="H7" s="23" t="s">
+      <c r="I7" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7" s="37" t="s">
+        <v>26</v>
+      </c>
+      <c r="K7" s="37"/>
+      <c r="L7" s="37"/>
+    </row>
+    <row r="8" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B8" s="42"/>
+      <c r="C8" s="42"/>
+      <c r="D8" s="21">
+        <v>1311</v>
+      </c>
+      <c r="E8" s="21">
+        <v>12345678</v>
+      </c>
+      <c r="F8" s="21" t="s">
+        <v>37</v>
+      </c>
+      <c r="G8" s="21" t="s">
+        <v>65</v>
+      </c>
+      <c r="H8" s="22" t="str">
+        <f ca="1">TEXT(NOW(), "mmdd")</f>
+        <v>0329</v>
+      </c>
+      <c r="I8" s="23" t="str">
+        <f ca="1">TEXT(NOW(), "hhmm")</f>
+        <v>2254</v>
+      </c>
+      <c r="J8" s="44" t="str">
+        <f ca="1">"["&amp;D8&amp;"]-["&amp;E8&amp;"]-["&amp;F8&amp;"]-["&amp;G8&amp;"]-["&amp;TEXT(H8,"0000")&amp;"]-["&amp;TEXT(I8,"0000")&amp;"]"</f>
+        <v>[1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254]</v>
+      </c>
+      <c r="K8" s="44"/>
+      <c r="L8" s="44"/>
+    </row>
+    <row r="9" spans="2:12" s="9" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+      <c r="D9" s="25"/>
+      <c r="E9" s="25"/>
+      <c r="F9" s="25"/>
+      <c r="G9" s="25"/>
+      <c r="H9" s="26"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="25"/>
+      <c r="K9" s="25"/>
+      <c r="L9" s="25"/>
+    </row>
+    <row r="10" spans="2:12" ht="66" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B10" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C10" s="28" t="s">
+        <v>120</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>103</v>
+      </c>
+      <c r="F10" s="50"/>
+      <c r="G10" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="H10" s="20" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="J10" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="K10" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="L10" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="I7" s="23" t="s">
-        <v>28</v>
-      </c>
-      <c r="J7" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="K7" s="40"/>
-      <c r="L7" s="40"/>
-    </row>
-    <row r="8" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="24">
-        <v>1311</v>
-      </c>
-      <c r="E8" s="24">
-        <v>12345678</v>
-      </c>
-      <c r="F8" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="G8" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="25" t="str">
-        <f ca="1">TEXT(NOW(), "mmdd")</f>
-        <v>0316</v>
-      </c>
-      <c r="I8" s="26" t="str">
-        <f ca="1">TEXT(NOW(), "hhmm")</f>
-        <v>0033</v>
-      </c>
-      <c r="J8" s="47" t="str">
-        <f ca="1">"["&amp;D8&amp;"]-["&amp;E8&amp;"]-["&amp;F8&amp;"]-["&amp;G8&amp;"]-["&amp;TEXT(H8,"0000")&amp;"]-["&amp;TEXT(I8,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033]</v>
-      </c>
-      <c r="K8" s="47"/>
-      <c r="L8" s="47"/>
-    </row>
-    <row r="9" spans="2:12" s="12" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="27"/>
-      <c r="C9" s="27"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="28"/>
-      <c r="F9" s="28"/>
-      <c r="G9" s="28"/>
-      <c r="H9" s="29"/>
-      <c r="I9" s="30"/>
-      <c r="J9" s="28"/>
-      <c r="K9" s="28"/>
-      <c r="L9" s="28"/>
-    </row>
-    <row r="10" spans="2:12" ht="33" x14ac:dyDescent="0.3">
-      <c r="B10" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="C10" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="D10" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="E10" s="23" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="23" t="s">
+    </row>
+    <row r="11" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B11" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="C11" s="30"/>
+      <c r="D11" s="30">
+        <v>10</v>
+      </c>
+      <c r="E11" s="47"/>
+      <c r="F11" s="48"/>
+      <c r="G11" s="30"/>
+      <c r="H11" s="20"/>
+      <c r="I11" s="20"/>
+      <c r="J11" s="20"/>
+      <c r="K11" s="20"/>
+      <c r="L11" s="31" t="str">
+        <f ca="1">C11&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / "&amp;E11&amp;" / 요청:"&amp;G11&amp;" / "&amp;D11)</f>
+        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254] /  / 요청: / 10</v>
+      </c>
+    </row>
+    <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B12" s="53" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="30"/>
+      <c r="D12" s="30">
+        <v>10</v>
+      </c>
+      <c r="E12" s="47">
+        <v>123</v>
+      </c>
+      <c r="F12" s="48"/>
+      <c r="G12" s="30">
+        <v>222</v>
+      </c>
+      <c r="H12" s="20"/>
+      <c r="I12" s="20"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="31" t="str">
+        <f ca="1">C12&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / "&amp;E12&amp;" / 요청:"&amp;G12&amp;" / "&amp;D12)</f>
+        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254] / 123 / 요청:222 / 10</v>
+      </c>
+    </row>
+    <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="53" t="s">
+        <v>60</v>
+      </c>
+      <c r="C13" s="20"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="20"/>
+      <c r="G13" s="20"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="30"/>
+      <c r="J13" s="20"/>
+      <c r="K13" s="20"/>
+      <c r="L13" s="31" t="str">
+        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H13="","{사유코드}",H13)&amp;" / 다음확인 "&amp;I13&amp;" (전화 1회 후)")</f>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B14" s="53" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="20"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="20"/>
+      <c r="H14" s="32"/>
+      <c r="I14" s="30"/>
+      <c r="J14" s="20"/>
+      <c r="K14" s="20"/>
+      <c r="L14" s="31" t="str">
+        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H14="","{사유코드}",H14)&amp;" / 다음확인 "&amp;I14&amp;" (전화 1회 후)")</f>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254] / {사유코드} / 다음확인  (전화 1회 후)</v>
+      </c>
+    </row>
+    <row r="15" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B15" s="53" t="s">
+        <v>0</v>
+      </c>
+      <c r="C15" s="20"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="30"/>
+      <c r="F15" s="20"/>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20"/>
+      <c r="I15" s="20"/>
+      <c r="J15" s="30" t="s">
+        <v>64</v>
+      </c>
+      <c r="K15" s="30"/>
+      <c r="L15" s="31" t="str">
+        <f ca="1">IF($J$8="","", "[D]"&amp;$J$8&amp;" / 결과:"&amp;E15&amp;" / 현재:"&amp;J15&amp;" / F/U:"&amp;K15)</f>
+        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254] / 결과: / 현재:처방확인 / F/U:</v>
+      </c>
+    </row>
+    <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B16" s="53" t="s">
         <v>31</v>
       </c>
-      <c r="G10" s="23" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="I10" s="23" t="s">
-        <v>29</v>
-      </c>
-      <c r="J10" s="23" t="s">
-        <v>5</v>
-      </c>
-      <c r="K10" s="23" t="s">
-        <v>33</v>
-      </c>
-      <c r="L10" s="23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="11" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="32" t="s">
-        <v>0</v>
-      </c>
-      <c r="C11" s="33"/>
-      <c r="D11" s="33">
-        <v>10</v>
-      </c>
-      <c r="E11" s="33"/>
-      <c r="F11" s="33"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="23"/>
-      <c r="I11" s="23"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="34" t="str">
-        <f ca="1">C11&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / 지금:"&amp;E11&amp;" / 근거:"&amp;F11&amp;" / 요청:"&amp;G11&amp;" / "&amp;D11)</f>
-        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033] / 지금: / 근거: / 요청: / 10</v>
-      </c>
-    </row>
-    <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-      <c r="G12" s="23"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="33"/>
-      <c r="J12" s="23"/>
-      <c r="K12" s="23"/>
-      <c r="L12" s="34" t="str">
-        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H12="","{사유코드}",H12)&amp;" / 다음확인 "&amp;I12&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="32" t="s">
+      <c r="C16" s="20"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="32"/>
+      <c r="F16" s="20"/>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20"/>
+      <c r="I16" s="20"/>
+      <c r="J16" s="20"/>
+      <c r="K16" s="20"/>
+      <c r="L16" s="31" t="str">
+        <f ca="1">IF($J$8="","", "(보고)"&amp;$J$8&amp;"/"&amp;E16&amp;IF(E16="","","/")&amp;"12")</f>
+        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254]/12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C17" s="36" t="s">
+        <v>67</v>
+      </c>
+      <c r="D17" s="36"/>
+      <c r="E17" s="37" t="s">
+        <v>68</v>
+      </c>
+      <c r="F17" s="37"/>
+      <c r="G17" s="37"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="J17" s="37"/>
+      <c r="K17" s="37"/>
+      <c r="L17" s="20"/>
+    </row>
+    <row r="18" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="29" t="s">
         <v>66</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-      <c r="G13" s="23"/>
-      <c r="H13" s="35"/>
-      <c r="I13" s="33"/>
-      <c r="J13" s="23"/>
-      <c r="K13" s="23"/>
-      <c r="L13" s="34" t="str">
-        <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H13="","{사유코드}",H13)&amp;" / 다음확인 "&amp;I13&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033] / {사유코드} / 다음확인  (전화 1회 후)</v>
-      </c>
-    </row>
-    <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="33"/>
-      <c r="F14" s="23"/>
-      <c r="G14" s="23"/>
-      <c r="H14" s="23"/>
-      <c r="I14" s="23"/>
-      <c r="J14" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="K14" s="33"/>
-      <c r="L14" s="34" t="str">
-        <f ca="1">IF($J$8="","", "[D]"&amp;$J$8&amp;" / 결과:"&amp;E14&amp;" / 현재:"&amp;J14&amp;" / F/U:"&amp;K14)</f>
-        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033] / 결과: / 현재:처방확인 / F/U:</v>
-      </c>
-    </row>
-    <row r="15" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="35"/>
-      <c r="F15" s="23"/>
-      <c r="G15" s="23"/>
-      <c r="H15" s="23"/>
-      <c r="I15" s="23"/>
-      <c r="J15" s="23"/>
-      <c r="K15" s="23"/>
-      <c r="L15" s="34" t="str">
-        <f ca="1">IF($J$8="","", "(보고)"&amp;$J$8&amp;"/"&amp;E15&amp;IF(E15="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033]/12</v>
-      </c>
-    </row>
-    <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="23" t="s">
-        <v>2</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>72</v>
-      </c>
-      <c r="D16" s="39"/>
-      <c r="E16" s="40" t="s">
-        <v>73</v>
-      </c>
-      <c r="F16" s="40"/>
-      <c r="G16" s="40"/>
-      <c r="H16" s="40"/>
-      <c r="I16" s="40" t="s">
-        <v>74</v>
-      </c>
-      <c r="J16" s="40"/>
-      <c r="K16" s="40"/>
-      <c r="L16" s="23"/>
-    </row>
-    <row r="17" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="32" t="s">
-        <v>71</v>
-      </c>
-      <c r="C17" s="41"/>
-      <c r="D17" s="41"/>
-      <c r="E17" s="41"/>
-      <c r="F17" s="41"/>
-      <c r="G17" s="41"/>
-      <c r="H17" s="41"/>
-      <c r="I17" s="41"/>
-      <c r="J17" s="41"/>
-      <c r="K17" s="41"/>
-      <c r="L17" s="34" t="str">
-        <f ca="1">IF($J$8="","", "[A][야간이음기록]"&amp;$J$8&amp;"/지금:"&amp;C17&amp;"/조치:"&amp;E17&amp;"/[D]"&amp;E17&amp;I17)</f>
-        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0316]-[0033]/지금:/조치:/[D]</v>
-      </c>
-    </row>
-    <row r="18" spans="2:12" s="8" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="19" spans="2:12" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B19" s="38" t="s">
-        <v>39</v>
-      </c>
-      <c r="C19" s="38"/>
-      <c r="D19" s="38"/>
-      <c r="E19" s="38"/>
-      <c r="F19" s="38"/>
-      <c r="G19" s="38"/>
-      <c r="H19" s="38"/>
-      <c r="I19" s="38"/>
-      <c r="J19" s="38"/>
-      <c r="K19" s="38"/>
-      <c r="L19" s="38"/>
+      <c r="C18" s="38"/>
+      <c r="D18" s="38"/>
+      <c r="E18" s="38"/>
+      <c r="F18" s="38"/>
+      <c r="G18" s="38"/>
+      <c r="H18" s="38"/>
+      <c r="I18" s="38"/>
+      <c r="J18" s="38"/>
+      <c r="K18" s="38"/>
+      <c r="L18" s="31" t="str">
+        <f ca="1">IF($J$8="","", "[A][야간이음기록]"&amp;$J$8&amp;"/지금:"&amp;C18&amp;"/조치:"&amp;E18&amp;"/[D]"&amp;E18&amp;I18)</f>
+        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254]/지금:/조치:/[D]</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B20" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
+  <mergeCells count="18">
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E12:F12"/>
     <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B19:L19"/>
-    <mergeCell ref="C16:D16"/>
-    <mergeCell ref="E16:H16"/>
-    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="B20:L20"/>
+    <mergeCell ref="C17:D17"/>
     <mergeCell ref="E17:H17"/>
     <mergeCell ref="I17:K17"/>
-    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="E18:H18"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="B2:L2"/>
@@ -1726,9 +1848,10 @@
     <mergeCell ref="B6:L6"/>
     <mergeCell ref="J8:L8"/>
     <mergeCell ref="J7:L7"/>
+    <mergeCell ref="E11:F11"/>
   </mergeCells>
   <phoneticPr fontId="5" type="noConversion"/>
-  <conditionalFormatting sqref="C11:D11">
+  <conditionalFormatting sqref="C11:D12">
     <cfRule type="expression" dxfId="2" priority="1">
       <formula>C11=12</formula>
     </cfRule>
@@ -1744,66 +1867,72 @@
   <legacyDrawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="10">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="11">
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000000000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D11 D15</xm:sqref>
+          <xm:sqref>D16 D11:D12</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$2:$B$14</xm:f>
           </x14:formula1>
-          <xm:sqref>H14</xm:sqref>
+          <xm:sqref>H15</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{72FFAC11-A338-427E-AF73-F7D83A85893C}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$J$2:$J$4</xm:f>
           </x14:formula1>
-          <xm:sqref>E15</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{54F24218-F1A5-4C39-A88F-EBBD79DE5CE8}">
-          <x14:formula1>
-            <xm:f>'02_코드목록'!$L$2:$L$11</xm:f>
-          </x14:formula1>
-          <xm:sqref>C11</xm:sqref>
+          <xm:sqref>E16</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{0D061B27-2ED0-4A89-8EF3-BCF08CD5E27F}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$B$2:$B$15</xm:f>
           </x14:formula1>
-          <xm:sqref>H12</xm:sqref>
+          <xm:sqref>H13</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{06472377-7060-4FB5-A3C2-0B85F9411171}">
           <x14:formula1>
             <xm:f>'02_코드목록'!$D$2</xm:f>
           </x14:formula1>
-          <xm:sqref>H13</xm:sqref>
+          <xm:sqref>H14</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0BB3FC94-3ED2-4C84-A3ED-2F30071EDD5F}">
           <x14:formula1>
-            <xm:f>'02_코드목록'!$B$23:$B$25</xm:f>
+            <xm:f>'02_코드목록'!$B$36:$B$38</xm:f>
           </x14:formula1>
           <xm:sqref>F3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{520AB831-8948-4772-A944-BFC6D5A572B3}">
           <x14:formula1>
-            <xm:f>'02_코드목록'!$E$23:$E$27</xm:f>
+            <xm:f>'02_코드목록'!$E$36:$E$40</xm:f>
           </x14:formula1>
           <xm:sqref>H3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F832BF57-460C-4480-8BA8-EBC99E7230DB}">
           <x14:formula1>
-            <xm:f>'02_코드목록'!$K$23:$K$26</xm:f>
+            <xm:f>'02_코드목록'!$K$36:$K$39</xm:f>
           </x14:formula1>
           <xm:sqref>D3</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{33E7ADC8-529F-4927-AAE9-C790AFD91F36}">
           <x14:formula1>
-            <xm:f>'02_코드목록'!$H$23:$H$28</xm:f>
+            <xm:f>'02_코드목록'!$H$36:$H$41</xm:f>
           </x14:formula1>
           <xm:sqref>D4</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{54F24218-F1A5-4C39-A88F-EBBD79DE5CE8}">
+          <x14:formula1>
+            <xm:f>'02_코드목록'!$L$16:$L$28</xm:f>
+          </x14:formula1>
+          <xm:sqref>C12</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5ED51441-025F-4310-B118-7A6E4E87943E}">
+          <x14:formula1>
+            <xm:f>'02_코드목록'!$L$2:$L$11</xm:f>
+          </x14:formula1>
+          <xm:sqref>C11</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -1814,7 +1943,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A1:M28"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12" style="3" customWidth="1"/>
@@ -1825,58 +1954,58 @@
     <col min="6" max="9" width="9" style="3"/>
     <col min="10" max="10" width="17.25" style="3" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="17.25" style="3" customWidth="1"/>
-    <col min="12" max="12" width="11.375" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13" style="3" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="38" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>6</v>
-      </c>
-      <c r="B1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>7</v>
       </c>
       <c r="G1" s="4"/>
       <c r="H1" s="4"/>
       <c r="J1" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>41</v>
-      </c>
-      <c r="M1" s="4"/>
+        <v>35</v>
+      </c>
+      <c r="L1" s="52" t="s">
+        <v>119</v>
+      </c>
+      <c r="M1" s="52"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>10</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F2" s="48" t="s">
-        <v>55</v>
-      </c>
-      <c r="G2" s="49"/>
-      <c r="H2" s="49"/>
+        <v>59</v>
+      </c>
+      <c r="F2" s="45" t="s">
+        <v>51</v>
+      </c>
+      <c r="G2" s="46"/>
+      <c r="H2" s="46"/>
       <c r="J2" s="5" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="K2" s="6"/>
       <c r="L2" s="4" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="M2" s="4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -1884,20 +2013,20 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" s="49"/>
-      <c r="G3" s="49"/>
-      <c r="H3" s="49"/>
+        <v>8</v>
+      </c>
+      <c r="F3" s="46"/>
+      <c r="G3" s="46"/>
+      <c r="H3" s="46"/>
       <c r="J3" s="5" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="K3" s="6"/>
       <c r="L3" s="4" t="s">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="M3" s="4" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.3">
@@ -1905,195 +2034,269 @@
         <v>12</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="49"/>
-      <c r="G4" s="49"/>
-      <c r="H4" s="49"/>
+        <v>9</v>
+      </c>
+      <c r="F4" s="46"/>
+      <c r="G4" s="46"/>
+      <c r="H4" s="46"/>
       <c r="J4" s="5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="K4" s="6"/>
       <c r="L4" s="4" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="M4" s="4" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L5" s="4" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="M5" s="4" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="M6" s="4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="4" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="M7" s="4" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" s="4" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="M8" s="4" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" s="4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="M9" s="4" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="M10" s="4" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11" s="4" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="M11" s="4" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" s="4" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" s="4" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="4" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A23" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="B23" s="9" t="s">
-        <v>83</v>
-      </c>
-      <c r="D23" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="3" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L16" s="51" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L17" s="51" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="18" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L18" s="51" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="19" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L19" s="51" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="20" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L20" s="51" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="21" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L21" s="51" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="22" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L22" s="51" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="23" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L23" s="51" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="24" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="K24" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L24" s="51" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="25" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L25" s="51" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="26" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L26" s="51" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="27" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L27" s="51" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="28" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="K28" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="L28" s="51" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A36" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>78</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="E36" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="G36" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H36" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="K36" s="4">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B37" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="H37" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="K37" s="4">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="B38" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="H38" s="11" t="s">
+        <v>94</v>
+      </c>
+      <c r="K38" s="4">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="39" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E39" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="H39" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K39" s="4">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="40" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="E40" s="4" t="s">
         <v>89</v>
       </c>
-      <c r="E23" s="7" t="s">
-        <v>90</v>
-      </c>
-      <c r="G23" s="11" t="s">
-        <v>102</v>
-      </c>
-      <c r="H23" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="J23" s="11" t="s">
-        <v>103</v>
-      </c>
-      <c r="K23" s="11">
+      <c r="H40" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H41" s="4" t="s">
         <v>92</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B24" s="9" t="s">
-        <v>84</v>
-      </c>
-      <c r="E24" s="7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H24" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="K24" s="11">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B25" s="9" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="7" t="s">
-        <v>92</v>
-      </c>
-      <c r="H25" s="14" t="s">
-        <v>99</v>
-      </c>
-      <c r="K25" s="11">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E26" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="H26" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="K26" s="11">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="E27" s="7" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27" s="11" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="H28" s="11" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>

--- a/documents/WeValue_현장ACD_메신저템플릿.xlsx
+++ b/documents/WeValue_현장ACD_메신저템플릿.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lds85\Desktop\임덕수\git\2026-QI\documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B77E4C1A-F2DF-4844-A85A-C49AFAE360AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{183160A4-6E50-4ED4-899D-6C382CB6E404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="25815" windowHeight="20985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="소통메신저 양식 자동완성" sheetId="2" r:id="rId1"/>
@@ -182,7 +182,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="124">
   <si>
     <t>D(완료)</t>
   </si>
@@ -556,13 +556,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>지금
-(핵심)
-근거
-(데이터)</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>[응급]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -580,6 +573,9 @@
   </si>
   <si>
     <t>[검사전/후]</t>
+  </si>
+  <si>
+    <t>[검사전/후]</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
@@ -636,6 +632,11 @@
   </si>
   <si>
     <t>A(14층전용)</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>지금(핵심)
+근거(데이터)</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -701,14 +702,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFF00"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
       <color theme="0"/>
       <name val="맑은 고딕"/>
       <family val="3"/>
@@ -759,6 +752,14 @@
       <charset val="129"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="9">
     <fill>
@@ -802,12 +803,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.79998168889431442"/>
+        <fgColor rgb="FF7030A0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="8">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -908,11 +909,35 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </left>
+      <right style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </right>
+      <top style="thin">
+        <color theme="0" tint="-0.14999847407452621"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -941,7 +966,7 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -950,9 +975,6 @@
     <xf numFmtId="176" fontId="3" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -968,7 +990,7 @@
     <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -995,9 +1017,6 @@
     <xf numFmtId="177" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1007,19 +1026,16 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="10" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="9" fillId="7" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1070,8 +1086,38 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1413,7 +1459,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="B1:L20"/>
+  <dimension ref="B1:L21"/>
   <sheetFormatPr defaultRowHeight="26.25" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4.75" style="1" customWidth="1"/>
@@ -1433,34 +1479,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:12" ht="66.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="33"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="34"/>
-      <c r="K1" s="34"/>
-      <c r="L1" s="34"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
     </row>
     <row r="2" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B2" s="41" t="s">
+      <c r="B2" s="38" t="s">
         <v>77</v>
       </c>
-      <c r="C2" s="41"/>
-      <c r="D2" s="41"/>
-      <c r="E2" s="41"/>
-      <c r="F2" s="41"/>
-      <c r="G2" s="41"/>
-      <c r="H2" s="41"/>
-      <c r="I2" s="41"/>
-      <c r="J2" s="41"/>
-      <c r="K2" s="41"/>
-      <c r="L2" s="41"/>
+      <c r="C2" s="38"/>
+      <c r="D2" s="38"/>
+      <c r="E2" s="38"/>
+      <c r="F2" s="38"/>
+      <c r="G2" s="38"/>
+      <c r="H2" s="38"/>
+      <c r="I2" s="38"/>
+      <c r="J2" s="38"/>
+      <c r="K2" s="38"/>
+      <c r="L2" s="38"/>
     </row>
     <row r="3" spans="2:12" s="10" customFormat="1" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B3" s="12" t="s">
@@ -1469,29 +1515,29 @@
       <c r="C3" s="12" t="s">
         <v>70</v>
       </c>
-      <c r="D3" s="13">
+      <c r="D3" s="58">
         <v>92</v>
       </c>
       <c r="E3" s="12" t="s">
         <v>71</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="58" t="s">
         <v>99</v>
       </c>
       <c r="G3" s="12" t="s">
         <v>72</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="58" t="s">
         <v>100</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="J3" s="15" t="s">
+      <c r="J3" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="K3" s="14"/>
-      <c r="L3" s="16" t="str">
+      <c r="K3" s="13"/>
+      <c r="L3" s="15" t="str">
         <f>"["&amp;D3&amp;"/"&amp;F3&amp;"/"&amp;H3&amp;"] "&amp;J3</f>
         <v>[92/나이트/B] 이OO</v>
       </c>
@@ -1503,344 +1549,357 @@
       <c r="C4" s="12" t="s">
         <v>75</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="D4" s="58" t="s">
         <v>90</v>
       </c>
-      <c r="E4" s="39" t="s">
+      <c r="E4" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="F4" s="39"/>
-      <c r="G4" s="40" t="s">
+      <c r="F4" s="36"/>
+      <c r="G4" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="H4" s="40"/>
-      <c r="I4" s="14" t="s">
+      <c r="H4" s="37"/>
+      <c r="I4" s="13" t="s">
         <v>82</v>
       </c>
-      <c r="J4" s="15" t="s">
+      <c r="J4" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="K4" s="14"/>
-      <c r="L4" s="16" t="str">
+      <c r="K4" s="13"/>
+      <c r="L4" s="15" t="str">
         <f>"["&amp;D4&amp;"/"&amp;G4&amp;"] "&amp;J4</f>
         <v>[141-MH/KJS] 이OO</v>
       </c>
     </row>
     <row r="5" spans="2:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B5" s="17"/>
-      <c r="C5" s="17"/>
-      <c r="D5" s="18"/>
-      <c r="E5" s="18"/>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="19"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="17"/>
+      <c r="G5" s="17"/>
+      <c r="H5" s="17"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="18"/>
     </row>
     <row r="6" spans="2:12" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B6" s="43" t="s">
+      <c r="B6" s="40" t="s">
         <v>101</v>
       </c>
-      <c r="C6" s="43"/>
-      <c r="D6" s="43"/>
-      <c r="E6" s="43"/>
-      <c r="F6" s="43"/>
-      <c r="G6" s="43"/>
-      <c r="H6" s="43"/>
-      <c r="I6" s="43"/>
-      <c r="J6" s="43"/>
-      <c r="K6" s="43"/>
-      <c r="L6" s="43"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="40"/>
+      <c r="K6" s="40"/>
+      <c r="L6" s="40"/>
     </row>
     <row r="7" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B7" s="42"/>
-      <c r="C7" s="42"/>
-      <c r="D7" s="20" t="s">
+      <c r="B7" s="39"/>
+      <c r="C7" s="39"/>
+      <c r="D7" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="H7" s="20" t="s">
+      <c r="H7" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="I7" s="20" t="s">
+      <c r="I7" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="J7" s="37" t="s">
+      <c r="J7" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="K7" s="37"/>
-      <c r="L7" s="37"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
     </row>
     <row r="8" spans="2:12" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="42"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="21">
+      <c r="B8" s="39"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="20">
         <v>1311</v>
       </c>
-      <c r="E8" s="21">
+      <c r="E8" s="20">
         <v>12345678</v>
       </c>
-      <c r="F8" s="21" t="s">
+      <c r="F8" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="21" t="s">
+      <c r="G8" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H8" s="22" t="str">
+      <c r="H8" s="21" t="str">
         <f ca="1">TEXT(NOW(), "mmdd")</f>
         <v>0329</v>
       </c>
-      <c r="I8" s="23" t="str">
+      <c r="I8" s="22" t="str">
         <f ca="1">TEXT(NOW(), "hhmm")</f>
-        <v>2254</v>
-      </c>
-      <c r="J8" s="44" t="str">
+        <v>2340</v>
+      </c>
+      <c r="J8" s="41" t="str">
         <f ca="1">"["&amp;D8&amp;"]-["&amp;E8&amp;"]-["&amp;F8&amp;"]-["&amp;G8&amp;"]-["&amp;TEXT(H8,"0000")&amp;"]-["&amp;TEXT(I8,"0000")&amp;"]"</f>
-        <v>[1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254]</v>
-      </c>
-      <c r="K8" s="44"/>
-      <c r="L8" s="44"/>
+        <v>[1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340]</v>
+      </c>
+      <c r="K8" s="41"/>
+      <c r="L8" s="41"/>
     </row>
     <row r="9" spans="2:12" s="9" customFormat="1" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="24"/>
-      <c r="C9" s="24"/>
-      <c r="D9" s="25"/>
-      <c r="E9" s="25"/>
-      <c r="F9" s="25"/>
-      <c r="G9" s="25"/>
-      <c r="H9" s="26"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="25"/>
-      <c r="K9" s="25"/>
-      <c r="L9" s="25"/>
+      <c r="B9" s="23"/>
+      <c r="C9" s="23"/>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="25"/>
+      <c r="I9" s="26"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
     </row>
     <row r="10" spans="2:12" ht="66" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="C10" s="28" t="s">
+      <c r="C10" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="E10" s="49" t="s">
-        <v>103</v>
-      </c>
-      <c r="F10" s="50"/>
-      <c r="G10" s="20" t="s">
+      <c r="E10" s="46" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="47"/>
+      <c r="G10" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="H10" s="20" t="s">
+      <c r="H10" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="I10" s="20" t="s">
+      <c r="I10" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="J10" s="20" t="s">
+      <c r="J10" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="K10" s="20" t="s">
+      <c r="K10" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="L10" s="20" t="s">
+      <c r="L10" s="19" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="11" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B11" s="53" t="s">
+      <c r="B11" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="30"/>
-      <c r="D11" s="30">
+      <c r="C11" s="59" t="s">
+        <v>42</v>
+      </c>
+      <c r="D11" s="28">
         <v>10</v>
       </c>
-      <c r="E11" s="47"/>
-      <c r="F11" s="48"/>
-      <c r="G11" s="30"/>
-      <c r="H11" s="20"/>
-      <c r="I11" s="20"/>
-      <c r="J11" s="20"/>
-      <c r="K11" s="20"/>
-      <c r="L11" s="31" t="str">
+      <c r="E11" s="44"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="19"/>
+      <c r="I11" s="19"/>
+      <c r="J11" s="19"/>
+      <c r="K11" s="19"/>
+      <c r="L11" s="29" t="str">
         <f ca="1">C11&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / "&amp;E11&amp;" / 요청:"&amp;G11&amp;" / "&amp;D11)</f>
-        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254] /  / 요청: / 10</v>
+        <v>[CVR][A][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340] /  / 요청: / 10</v>
       </c>
     </row>
     <row r="12" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B12" s="53" t="s">
+      <c r="B12" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="30"/>
-      <c r="D12" s="30">
+      <c r="C12" s="59" t="s">
+        <v>107</v>
+      </c>
+      <c r="D12" s="28">
         <v>10</v>
       </c>
-      <c r="E12" s="47">
-        <v>123</v>
-      </c>
-      <c r="F12" s="48"/>
-      <c r="G12" s="30">
-        <v>222</v>
-      </c>
-      <c r="H12" s="20"/>
-      <c r="I12" s="20"/>
-      <c r="J12" s="20"/>
-      <c r="K12" s="20"/>
-      <c r="L12" s="31" t="str">
+      <c r="E12" s="44"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="19"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="19"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="29" t="str">
         <f ca="1">C12&amp;IF($J$8="","", "[A]"&amp;$J$8&amp;" / "&amp;E12&amp;" / 요청:"&amp;G12&amp;" / "&amp;D12)</f>
-        <v>[A][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254] / 123 / 요청:222 / 10</v>
+        <v>[검사전/후][A][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340] /  / 요청: / 10</v>
       </c>
     </row>
     <row r="13" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="19" t="s">
         <v>60</v>
       </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="20"/>
-      <c r="G13" s="20"/>
-      <c r="H13" s="32"/>
-      <c r="I13" s="30"/>
-      <c r="J13" s="20"/>
-      <c r="K13" s="20"/>
-      <c r="L13" s="31" t="str">
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="28"/>
+      <c r="J13" s="19"/>
+      <c r="K13" s="19"/>
+      <c r="L13" s="29" t="str">
         <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H13="","{사유코드}",H13)&amp;" / 다음확인 "&amp;I13&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="14" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B14" s="53" t="s">
+      <c r="B14" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="20"/>
-      <c r="F14" s="20"/>
-      <c r="G14" s="20"/>
-      <c r="H14" s="32"/>
-      <c r="I14" s="30"/>
-      <c r="J14" s="20"/>
-      <c r="K14" s="20"/>
-      <c r="L14" s="31" t="str">
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="19"/>
+      <c r="K14" s="19"/>
+      <c r="L14" s="29" t="str">
         <f ca="1">IF($J$8="","", "[C]"&amp;$J$8&amp;" / "&amp;IF(H14="","{사유코드}",H14)&amp;" / 다음확인 "&amp;I14&amp;" (전화 1회 후)")</f>
-        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254] / {사유코드} / 다음확인  (전화 1회 후)</v>
+        <v>[C][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340] / {사유코드} / 다음확인  (전화 1회 후)</v>
       </c>
     </row>
     <row r="15" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="53" t="s">
+      <c r="B15" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C15" s="20"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="30"/>
-      <c r="F15" s="20"/>
-      <c r="G15" s="20"/>
-      <c r="H15" s="20"/>
-      <c r="I15" s="20"/>
-      <c r="J15" s="30" t="s">
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="28"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+      <c r="H15" s="19"/>
+      <c r="I15" s="19"/>
+      <c r="J15" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="K15" s="30"/>
-      <c r="L15" s="31" t="str">
+      <c r="K15" s="28"/>
+      <c r="L15" s="29" t="str">
         <f ca="1">IF($J$8="","", "[D]"&amp;$J$8&amp;" / 결과:"&amp;E15&amp;" / 현재:"&amp;J15&amp;" / F/U:"&amp;K15)</f>
-        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254] / 결과: / 현재:처방확인 / F/U:</v>
+        <v>[D][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340] / 결과: / 현재:처방확인 / F/U:</v>
       </c>
     </row>
     <row r="16" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B16" s="53" t="s">
+      <c r="B16" s="50" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="20"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="20"/>
-      <c r="G16" s="20"/>
-      <c r="H16" s="20"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
-      <c r="K16" s="20"/>
-      <c r="L16" s="31" t="str">
+      <c r="C16" s="50"/>
+      <c r="D16" s="50"/>
+      <c r="E16" s="60"/>
+      <c r="F16" s="50"/>
+      <c r="G16" s="50"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+      <c r="J16" s="50"/>
+      <c r="K16" s="50"/>
+      <c r="L16" s="51" t="str">
         <f ca="1">IF($J$8="","", "(보고)"&amp;$J$8&amp;"/"&amp;E16&amp;IF(E16="","","/")&amp;"12")</f>
-        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254]/12</v>
-      </c>
-    </row>
-    <row r="17" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="20" t="s">
+        <v>(보고)[1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340]/12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:12" s="9" customFormat="1" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B17" s="55"/>
+      <c r="C17" s="55"/>
+      <c r="D17" s="55"/>
+      <c r="E17" s="56"/>
+      <c r="F17" s="55"/>
+      <c r="G17" s="55"/>
+      <c r="H17" s="55"/>
+      <c r="I17" s="55"/>
+      <c r="J17" s="55"/>
+      <c r="K17" s="55"/>
+      <c r="L17" s="57"/>
+    </row>
+    <row r="18" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B18" s="52" t="s">
         <v>1</v>
       </c>
-      <c r="C17" s="36" t="s">
+      <c r="C18" s="53" t="s">
         <v>67</v>
       </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="37" t="s">
+      <c r="D18" s="53"/>
+      <c r="E18" s="54" t="s">
         <v>68</v>
       </c>
-      <c r="F17" s="37"/>
-      <c r="G17" s="37"/>
-      <c r="H17" s="37"/>
-      <c r="I17" s="37" t="s">
+      <c r="F18" s="54"/>
+      <c r="G18" s="54"/>
+      <c r="H18" s="54"/>
+      <c r="I18" s="54" t="s">
         <v>69</v>
       </c>
-      <c r="J17" s="37"/>
-      <c r="K17" s="37"/>
-      <c r="L17" s="20"/>
-    </row>
-    <row r="18" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B18" s="29" t="s">
+      <c r="J18" s="54"/>
+      <c r="K18" s="54"/>
+      <c r="L18" s="52"/>
+    </row>
+    <row r="19" spans="2:12" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B19" s="27" t="s">
         <v>66</v>
       </c>
-      <c r="C18" s="38"/>
-      <c r="D18" s="38"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="38"/>
-      <c r="G18" s="38"/>
-      <c r="H18" s="38"/>
-      <c r="I18" s="38"/>
-      <c r="J18" s="38"/>
-      <c r="K18" s="38"/>
-      <c r="L18" s="31" t="str">
-        <f ca="1">IF($J$8="","", "[A][야간이음기록]"&amp;$J$8&amp;"/지금:"&amp;C18&amp;"/조치:"&amp;E18&amp;"/[D]"&amp;E18&amp;I18)</f>
-        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2254]/지금:/조치:/[D]</v>
-      </c>
-    </row>
-    <row r="20" spans="2:12" ht="110.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B20" s="35" t="s">
+      <c r="C19" s="35"/>
+      <c r="D19" s="35"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="29" t="str">
+        <f ca="1">IF($J$8="","", "[A][야간이음기록]"&amp;$J$8&amp;"/지금:"&amp;C19&amp;"/조치:"&amp;E19&amp;"/[D]"&amp;E19&amp;I19)</f>
+        <v>[A][야간이음기록][1311]-[12345678]-[가나다]-[박OO]-[0329]-[2340]/지금:/조치:/[D]</v>
+      </c>
+    </row>
+    <row r="21" spans="2:12" ht="57.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B21" s="33" t="s">
         <v>36</v>
       </c>
-      <c r="C20" s="35"/>
-      <c r="D20" s="35"/>
-      <c r="E20" s="35"/>
-      <c r="F20" s="35"/>
-      <c r="G20" s="35"/>
-      <c r="H20" s="35"/>
-      <c r="I20" s="35"/>
-      <c r="J20" s="35"/>
-      <c r="K20" s="35"/>
-      <c r="L20" s="35"/>
+      <c r="C21" s="33"/>
+      <c r="D21" s="33"/>
+      <c r="E21" s="33"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="33"/>
+      <c r="J21" s="33"/>
+      <c r="K21" s="33"/>
+      <c r="L21" s="33"/>
     </row>
   </sheetData>
   <mergeCells count="18">
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="B1:L1"/>
-    <mergeCell ref="B20:L20"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="E17:H17"/>
-    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="B21:L21"/>
+    <mergeCell ref="C18:D18"/>
     <mergeCell ref="E18:H18"/>
     <mergeCell ref="I18:K18"/>
-    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E19:H19"/>
+    <mergeCell ref="I19:K19"/>
+    <mergeCell ref="C19:D19"/>
     <mergeCell ref="E4:F4"/>
     <mergeCell ref="G4:H4"/>
     <mergeCell ref="B2:L2"/>
@@ -1872,7 +1931,7 @@
           <x14:formula1>
             <xm:f>'02_코드목록'!$A$2:$A$4</xm:f>
           </x14:formula1>
-          <xm:sqref>D16 D11:D12</xm:sqref>
+          <xm:sqref>D16:D17 D11:D12</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{00000000-0002-0000-0100-000001000000}">
           <x14:formula1>
@@ -1884,7 +1943,7 @@
           <x14:formula1>
             <xm:f>'02_코드목록'!$J$2:$J$4</xm:f>
           </x14:formula1>
-          <xm:sqref>E16</xm:sqref>
+          <xm:sqref>E16:E17</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" xr:uid="{0D061B27-2ED0-4A89-8EF3-BCF08CD5E27F}">
           <x14:formula1>
@@ -1977,10 +2036,10 @@
       <c r="J1" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="L1" s="52" t="s">
+      <c r="L1" s="49" t="s">
         <v>119</v>
       </c>
-      <c r="M1" s="52"/>
+      <c r="M1" s="49"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
@@ -1992,11 +2051,11 @@
       <c r="D2" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="F2" s="45" t="s">
+      <c r="F2" s="42" t="s">
         <v>51</v>
       </c>
-      <c r="G2" s="46"/>
-      <c r="H2" s="46"/>
+      <c r="G2" s="43"/>
+      <c r="H2" s="43"/>
       <c r="J2" s="5" t="s">
         <v>32</v>
       </c>
@@ -2015,9 +2074,9 @@
       <c r="B3" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="F3" s="46"/>
-      <c r="G3" s="46"/>
-      <c r="H3" s="46"/>
+      <c r="F3" s="43"/>
+      <c r="G3" s="43"/>
+      <c r="H3" s="43"/>
       <c r="J3" s="5" t="s">
         <v>33</v>
       </c>
@@ -2036,9 +2095,9 @@
       <c r="B4" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="F4" s="46"/>
-      <c r="G4" s="46"/>
-      <c r="H4" s="46"/>
+      <c r="F4" s="43"/>
+      <c r="G4" s="43"/>
+      <c r="H4" s="43"/>
       <c r="J4" s="5" t="s">
         <v>34</v>
       </c>
@@ -2151,42 +2210,42 @@
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="L16" s="51" t="s">
+      <c r="L16" s="48" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="17" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L17" s="48" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="17" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L17" s="51" t="s">
+    <row r="18" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L18" s="48" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="18" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L18" s="51" t="s">
+    <row r="19" spans="11:12" x14ac:dyDescent="0.3">
+      <c r="L19" s="48" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L19" s="51" t="s">
-        <v>107</v>
-      </c>
-    </row>
     <row r="20" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L20" s="51" t="s">
+      <c r="L20" s="48" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="21" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L21" s="51" t="s">
+      <c r="L21" s="48" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="22" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L22" s="51" t="s">
+      <c r="L22" s="48" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="23" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L23" s="51" t="s">
+      <c r="L23" s="48" t="s">
         <v>111</v>
       </c>
     </row>
@@ -2194,22 +2253,22 @@
       <c r="K24" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="L24" s="51" t="s">
+      <c r="L24" s="48" t="s">
         <v>112</v>
       </c>
     </row>
     <row r="25" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L25" s="51" t="s">
+      <c r="L25" s="48" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="26" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L26" s="51" t="s">
+      <c r="L26" s="48" t="s">
         <v>114</v>
       </c>
     </row>
     <row r="27" spans="11:12" x14ac:dyDescent="0.3">
-      <c r="L27" s="51" t="s">
+      <c r="L27" s="48" t="s">
         <v>115</v>
       </c>
     </row>
@@ -2217,7 +2276,7 @@
       <c r="K28" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="L28" s="51" t="s">
+      <c r="L28" s="48" t="s">
         <v>116</v>
       </c>
     </row>
